--- a/ZonasEscolares/excels/CALLAO-CALLAO-CALLAO.xlsx
+++ b/ZonasEscolares/excels/CALLAO-CALLAO-CALLAO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/CALLAO-CALLAO-CALLAO.xlsx
+++ b/ZonasEscolares/excels/CALLAO-CALLAO-CALLAO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>62 PASITOS DE JESUS</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.05516</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.13472</v>
-      </c>
-      <c r="I2" t="n">
-        <v>339</v>
-      </c>
-      <c r="J2" t="n">
-        <v>17</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.05516</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.13472</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>64 DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.05287</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.13030999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>301</v>
-      </c>
-      <c r="J3" t="n">
-        <v>13</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.05287</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.13031</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>67</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.0218</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.13679999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>135</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.0218</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.1368</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>071 RETOÑITOS DE LA VIRGEN DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.043279</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.113979</v>
-      </c>
-      <c r="I5" t="n">
-        <v>257</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.043279</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.113979</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>69 MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.03731</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.09663999999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>218</v>
-      </c>
-      <c r="J6" t="n">
-        <v>12</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.03731</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.09664</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>073 SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.01661</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.09039</v>
-      </c>
-      <c r="I7" t="n">
-        <v>268</v>
-      </c>
-      <c r="J7" t="n">
-        <v>11</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.01661</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.09039</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>76 MI AMIGO JESUS</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.04083</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.12267</v>
-      </c>
-      <c r="I8" t="n">
-        <v>331</v>
-      </c>
-      <c r="J8" t="n">
-        <v>13</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.04083</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.12267</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>77 SANTISIMA VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.01001</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.10459</v>
-      </c>
-      <c r="I9" t="n">
-        <v>271</v>
-      </c>
-      <c r="J9" t="n">
-        <v>13</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.01001</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.10459</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>JUAN INGUNZA VALDIVIA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.01202</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.0979</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1275</v>
-      </c>
-      <c r="J10" t="n">
-        <v>56</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.01202</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.0979</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>78 AMIGUITOS DE SAN MARTIN</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.03371</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.09884</v>
-      </c>
-      <c r="I11" t="n">
-        <v>239</v>
-      </c>
-      <c r="J11" t="n">
-        <v>11</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.03371</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.09884</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>80 LOS NIÑOS DE JESUS</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.99643</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.12439999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>260</v>
-      </c>
-      <c r="J12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.99643</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.1244</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>4008 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.05278</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.10824</v>
-      </c>
-      <c r="I13" t="n">
-        <v>428</v>
-      </c>
-      <c r="J13" t="n">
-        <v>16</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.05278</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.10824</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>94 MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.04614</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.10393000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>294</v>
-      </c>
-      <c r="J14" t="n">
-        <v>13</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.04614</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.10393</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>84 NIÑA MARIA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.0159</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.10012999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>304</v>
-      </c>
-      <c r="J15" t="n">
-        <v>13</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.0159</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.10013</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>85 NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.01256</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.10178000000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>312</v>
-      </c>
-      <c r="J16" t="n">
-        <v>13</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.01256</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.10178</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>86 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.01318</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.10303</v>
-      </c>
-      <c r="I17" t="n">
-        <v>336</v>
-      </c>
-      <c r="J17" t="n">
-        <v>15</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.01318</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.10303</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>87 SANTA ROSA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.01653</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.1014</v>
-      </c>
-      <c r="I18" t="n">
-        <v>285</v>
-      </c>
-      <c r="J18" t="n">
-        <v>13</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.01653</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.1014</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>5023 ABELARDO GAMARRA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.05689</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.12657</v>
-      </c>
-      <c r="I19" t="n">
-        <v>568</v>
-      </c>
-      <c r="J19" t="n">
-        <v>25</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.05689</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.12657</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>100 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.00085</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.10856</v>
-      </c>
-      <c r="I20" t="n">
-        <v>249</v>
-      </c>
-      <c r="J20" t="n">
-        <v>11</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.00085</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.10856</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>109 DIVINO JESUS</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.02312</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.09538000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>206</v>
-      </c>
-      <c r="J21" t="n">
-        <v>10</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.02312</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.09538</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>111 MI PEQUEÑO PARAISO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.02819</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.09627</v>
-      </c>
-      <c r="I22" t="n">
-        <v>298</v>
-      </c>
-      <c r="J22" t="n">
-        <v>12</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.02819</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.09627</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>112 MEDALLITA MILAGROSA</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-11.99638</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.11823</v>
-      </c>
-      <c r="I23" t="n">
-        <v>207</v>
-      </c>
-      <c r="J23" t="n">
-        <v>8</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-11.99638</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.11823</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>115 VIRGEN DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.02384</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.09334</v>
-      </c>
-      <c r="I24" t="n">
-        <v>279</v>
-      </c>
-      <c r="J24" t="n">
-        <v>12</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.02384</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.09334</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>5040 PEDRO RUIZ</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.05041</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.10393000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>501</v>
-      </c>
-      <c r="J25" t="n">
-        <v>28</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.05041</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.10393</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>4001 DOS DE MAYO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.06411</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-77.15228999999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>867</v>
-      </c>
-      <c r="J26" t="n">
-        <v>48</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.06411</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-77.15229</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>4007 VIRGEN DEL PILAR</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.0549</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-77.11255</v>
-      </c>
-      <c r="I27" t="n">
-        <v>480</v>
-      </c>
-      <c r="J27" t="n">
-        <v>23</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.0549</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-77.11255</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>5032 ENRIQUE DEL HORME</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.05201</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-77.10136</v>
-      </c>
-      <c r="I28" t="n">
-        <v>425</v>
-      </c>
-      <c r="J28" t="n">
-        <v>21</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.05201</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-77.10136</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>5001 LUISA DE SABOGAL</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.06053</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-77.14445000000001</v>
-      </c>
-      <c r="I29" t="n">
-        <v>403</v>
-      </c>
-      <c r="J29" t="n">
-        <v>19</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.06053</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-77.14445</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>4006 SANTA ROSA DE AMERICA</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.05609</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-77.11615</v>
-      </c>
-      <c r="I30" t="n">
-        <v>608</v>
-      </c>
-      <c r="J30" t="n">
-        <v>30</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.05609</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-77.11615</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>92 LOS NIÑITOS DE SANTA ROSA</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.05338</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-77.1198</v>
-      </c>
-      <c r="I31" t="n">
-        <v>201</v>
-      </c>
-      <c r="J31" t="n">
-        <v>10</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.05338</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-77.1198</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.02478</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-77.12934</v>
-      </c>
-      <c r="I32" t="n">
-        <v>232</v>
-      </c>
-      <c r="J32" t="n">
-        <v>14</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.02478</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-77.12934</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>5031 CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.04287</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-77.10235</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1086</v>
-      </c>
-      <c r="J33" t="n">
-        <v>49</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.04287</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-77.10235</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>5019 AUGUSTO CAZORLA</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.05306</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-77.13395</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1122</v>
-      </c>
-      <c r="J34" t="n">
-        <v>58</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.05306</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-77.13395</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>5024 FRANCISCO MIRO QUESADA CANTUARIAS</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.05389</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-77.12877</v>
-      </c>
-      <c r="I35" t="n">
-        <v>539</v>
-      </c>
-      <c r="J35" t="n">
-        <v>24</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.05389</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-77.12877</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>REPUBLICA DE VENEZUELA</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-12.05177</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-77.13086</v>
-      </c>
-      <c r="I36" t="n">
-        <v>814</v>
-      </c>
-      <c r="J36" t="n">
-        <v>63</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.05177</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-77.13086</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>4010 HERMANOS RAFAEL SAMUEL Y EMILIO MOISES GOMEZ PAQUIYAURI</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-11.97657</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-77.12293</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1037</v>
-      </c>
-      <c r="J37" t="n">
-        <v>49</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-11.97657</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-77.12293</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>4011 LA TABOADA DE LAS FRESAS</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.00276</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-77.11283</v>
-      </c>
-      <c r="I38" t="n">
-        <v>430</v>
-      </c>
-      <c r="J38" t="n">
-        <v>16</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.00276</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-77.11283</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>4016 NESTOR GAMBETA BONATTI</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-12.0434</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-77.11369999999999</v>
-      </c>
-      <c r="I39" t="n">
-        <v>789</v>
-      </c>
-      <c r="J39" t="n">
-        <v>38</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.0434</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-77.1137</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>789</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>4018 ABRAHAM VALDELOMAR</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-12.04283</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-77.11144</v>
-      </c>
-      <c r="I40" t="n">
-        <v>765</v>
-      </c>
-      <c r="J40" t="n">
-        <v>40</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.04283</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-77.11144</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>5003 VIRGEN DE LA INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-12.06318</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-77.14344</v>
-      </c>
-      <c r="I41" t="n">
-        <v>306</v>
-      </c>
-      <c r="J41" t="n">
-        <v>15</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-12.06318</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-77.14344</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>5005 GENMO DON JOSE DE SAN MARTIN</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-12.05954</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-77.13717</v>
-      </c>
-      <c r="I42" t="n">
-        <v>723</v>
-      </c>
-      <c r="J42" t="n">
-        <v>34</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-12.05954</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-77.13717</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>5006 ALBERTO SECADA</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-12.05868</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-77.14027</v>
-      </c>
-      <c r="I43" t="n">
-        <v>329</v>
-      </c>
-      <c r="J43" t="n">
-        <v>15</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-12.05868</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-77.14027</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>5007 NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-12.05276</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-77.14019999999999</v>
-      </c>
-      <c r="I44" t="n">
-        <v>592</v>
-      </c>
-      <c r="J44" t="n">
-        <v>36</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-12.05276</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-77.1402</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>5042 JUAN FRANCISCO DE LA BODEGA Y QUADRA</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-12.04569</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-77.11355</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1073</v>
-      </c>
-      <c r="J45" t="n">
-        <v>49</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-12.04569</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-77.11355</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>5046 JOSE GALVEZ EGUSQUIZA</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-12.04398</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-77.12434</v>
-      </c>
-      <c r="I46" t="n">
-        <v>511</v>
-      </c>
-      <c r="J46" t="n">
-        <v>26</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-12.04398</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-77.12434</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>5048 MARISCAL RAMON CASTILLA</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-12.04143</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-77.12345000000001</v>
-      </c>
-      <c r="I47" t="n">
-        <v>1209</v>
-      </c>
-      <c r="J47" t="n">
-        <v>70</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-12.04143</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-77.12345</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1209</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>5049 EMMA DETTMANN DE GUTIERREZ</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-12.05066</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-77.09526</v>
-      </c>
-      <c r="I48" t="n">
-        <v>781</v>
-      </c>
-      <c r="J48" t="n">
-        <v>45</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-12.05066</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-77.09526</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>5036 RAFAEL BELAUNDE DIEZ CANSECO</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-12.03769</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-77.09641000000001</v>
-      </c>
-      <c r="I49" t="n">
-        <v>664</v>
-      </c>
-      <c r="J49" t="n">
-        <v>27</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-12.03769</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-77.09641</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>5037 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-12.02282</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-77.13737999999999</v>
-      </c>
-      <c r="I50" t="n">
-        <v>534</v>
-      </c>
-      <c r="J50" t="n">
-        <v>25</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-12.02282</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-77.13738</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>5010 VIRGEN DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-12.04644</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-77.10265</v>
-      </c>
-      <c r="I51" t="n">
-        <v>392</v>
-      </c>
-      <c r="J51" t="n">
-        <v>17</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-12.04644</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-77.10265</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>5076 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-11.9433</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-77.1326</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2339</v>
-      </c>
-      <c r="J52" t="n">
-        <v>112</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-11.9433</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-77.1326</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2339</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>5075 INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-12.03424</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-77.09829000000001</v>
-      </c>
-      <c r="I53" t="n">
-        <v>523</v>
-      </c>
-      <c r="J53" t="n">
-        <v>23</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-12.03424</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-77.09829</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>5074 ALCIDES SPELUCIN VEGA</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-12.00959</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-77.09623999999999</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1579</v>
-      </c>
-      <c r="J54" t="n">
-        <v>63</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-12.00959</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-77.09624</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>5033 LAS 200 MILLAS</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-11.9944</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-77.12350000000001</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1231</v>
-      </c>
-      <c r="J55" t="n">
-        <v>56</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-11.9944</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-77.1235</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>5026 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-12.01984</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-77.09148999999999</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1969</v>
-      </c>
-      <c r="J56" t="n">
-        <v>87</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-12.01984</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-77.09149</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>5078 JOSE A. QUIÑONES GONZALES</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-12.0528</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-77.12218</v>
-      </c>
-      <c r="I57" t="n">
-        <v>232</v>
-      </c>
-      <c r="J57" t="n">
-        <v>11</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-12.0528</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-77.12218</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>5079 JORGE CHAVEZ DARNELL</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-12.0174</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-77.09675</v>
-      </c>
-      <c r="I58" t="n">
-        <v>626</v>
-      </c>
-      <c r="J58" t="n">
-        <v>29</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-12.0174</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-77.09675</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>5082 SARITA COLONIA</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-12.023593</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-77.1332</v>
-      </c>
-      <c r="I59" t="n">
-        <v>956</v>
-      </c>
-      <c r="J59" t="n">
-        <v>48</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-12.023593</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-77.1332</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>5083 SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-12.01038</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-77.10504</v>
-      </c>
-      <c r="I60" t="n">
-        <v>732</v>
-      </c>
-      <c r="J60" t="n">
-        <v>31</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-12.01038</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-77.10504</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>5080 SOR ANA DE LOS ANGELES</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-12.01107</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-77.10339</v>
-      </c>
-      <c r="I61" t="n">
-        <v>3081</v>
-      </c>
-      <c r="J61" t="n">
-        <v>134</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-12.01107</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-77.10339</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>5084 CARLOS PHILLIPS</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-12.017055</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-77.090428</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1101</v>
-      </c>
-      <c r="J62" t="n">
-        <v>44</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-12.017055</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-77.090428</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>5085 RAMIRO PRIALE PRIALE</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-12.01514</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-77.09056</v>
-      </c>
-      <c r="I63" t="n">
-        <v>1302</v>
-      </c>
-      <c r="J63" t="n">
-        <v>62</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-12.01514</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-77.09056</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>5089 VIRGEN MARIA</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-11.99932</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-77.10861</v>
-      </c>
-      <c r="I64" t="n">
-        <v>722</v>
-      </c>
-      <c r="J64" t="n">
-        <v>27</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-11.99932</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-77.10861</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>5092 SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-12.02346</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-77.10115999999999</v>
-      </c>
-      <c r="I65" t="n">
-        <v>521</v>
-      </c>
-      <c r="J65" t="n">
-        <v>24</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-12.02346</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-77.10116</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>5095 JULIO RAMON RIBEYRO</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-12.0253</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-77.09650000000001</v>
-      </c>
-      <c r="I66" t="n">
-        <v>1437</v>
-      </c>
-      <c r="J66" t="n">
-        <v>64</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-12.0253</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-77.0965</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1437</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>5097 SAN JUAN MACIAS</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-11.99755</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-77.11748</v>
-      </c>
-      <c r="I67" t="n">
-        <v>1471</v>
-      </c>
-      <c r="J67" t="n">
-        <v>65</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-11.99755</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-77.11748</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1471</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>HEROINAS TOLEDO</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-12.06186</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-77.13567</v>
-      </c>
-      <c r="I68" t="n">
-        <v>449</v>
-      </c>
-      <c r="J68" t="n">
-        <v>47</v>
-      </c>
-      <c r="K68" t="n">
-        <v>1</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-12.06186</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-77.13567</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>POLITECNICO NACIONAL DEL CALLAO</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-12.044294</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-77.099361</v>
-      </c>
-      <c r="I69" t="n">
-        <v>1587</v>
-      </c>
-      <c r="J69" t="n">
-        <v>87</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-12.044294</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-77.099361</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1587</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>JORGE BASADRE GROHMAN</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-12.06236</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-77.13567</v>
-      </c>
-      <c r="I70" t="n">
-        <v>410</v>
-      </c>
-      <c r="J70" t="n">
-        <v>23</v>
-      </c>
-      <c r="K70" t="n">
-        <v>1</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-12.06236</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-77.13567</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>5099 RICARDO PALMA</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-12.02017</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-77.09931</v>
-      </c>
-      <c r="I71" t="n">
-        <v>687</v>
-      </c>
-      <c r="J71" t="n">
-        <v>35</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-12.02017</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-77.09931</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>98 NIÑITO JESUS DE PRAGA</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-11.94224</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-77.13399</v>
-      </c>
-      <c r="I72" t="n">
-        <v>310</v>
-      </c>
-      <c r="J72" t="n">
-        <v>12</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-11.94224</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-77.13399</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>JUAN LINARES ROJAS</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-11.97227</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-77.1229</v>
-      </c>
-      <c r="I73" t="n">
-        <v>792</v>
-      </c>
-      <c r="J73" t="n">
-        <v>41</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-11.97227</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-77.1229</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>JOSE GALVEZ</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-12.05679</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-77.13601</v>
-      </c>
-      <c r="I74" t="n">
-        <v>377</v>
-      </c>
-      <c r="J74" t="n">
-        <v>36</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-12.05679</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-77.13601</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>JUNIOR CESAR DE LOS RIOS</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-12.05347</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-77.12979</v>
-      </c>
-      <c r="I75" t="n">
-        <v>869</v>
-      </c>
-      <c r="J75" t="n">
-        <v>59</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-12.05347</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-77.12979</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-12.01704</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-77.09554</v>
-      </c>
-      <c r="I76" t="n">
-        <v>821</v>
-      </c>
-      <c r="J76" t="n">
-        <v>45</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-12.01704</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-77.09554</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>SANTA CRUZ</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-12.03214</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-77.09748</v>
-      </c>
-      <c r="I77" t="n">
-        <v>1051</v>
-      </c>
-      <c r="J77" t="n">
-        <v>59</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-12.03214</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-77.09748</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>NIÑO JESUS MARISCAL CHAPERITO</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-12.02095</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-77.09563</v>
-      </c>
-      <c r="I78" t="n">
-        <v>260</v>
-      </c>
-      <c r="J78" t="n">
-        <v>29</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-12.02095</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-77.09563</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-12.02196</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-77.09209</v>
-      </c>
-      <c r="I79" t="n">
-        <v>347</v>
-      </c>
-      <c r="J79" t="n">
-        <v>28</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-12.02196</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-77.09209</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>MERIDIONAL SANTA ANA</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-12.04089</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-77.1249</v>
-      </c>
-      <c r="I80" t="n">
-        <v>480</v>
-      </c>
-      <c r="J80" t="n">
-        <v>25</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-12.04089</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-77.1249</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>JERUSALEN</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-12.04123</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-77.10048</v>
-      </c>
-      <c r="I81" t="n">
-        <v>274</v>
-      </c>
-      <c r="J81" t="n">
-        <v>25</v>
-      </c>
-      <c r="K81" t="n">
-        <v>1</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-12.04123</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-77.10048</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>SAN BENITO DE PALERMO</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-11.99852</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-77.11808000000001</v>
-      </c>
-      <c r="I82" t="n">
-        <v>417</v>
-      </c>
-      <c r="J82" t="n">
-        <v>24</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-11.99852</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-77.11808</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>JEAN CALVIN LEFRANC</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-12.00717</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-77.10353000000001</v>
-      </c>
-      <c r="I83" t="n">
-        <v>235</v>
-      </c>
-      <c r="J83" t="n">
-        <v>24</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-12.00717</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-77.10353</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>JORDAN DE JESUS</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-11.99636</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-77.12294</v>
-      </c>
-      <c r="I84" t="n">
-        <v>219</v>
-      </c>
-      <c r="J84" t="n">
-        <v>14</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-11.99636</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-77.12294</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>FLORENCE NIGHTINGALE</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-12.01716</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-77.09765</v>
-      </c>
-      <c r="I85" t="n">
-        <v>327</v>
-      </c>
-      <c r="J85" t="n">
-        <v>21</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-12.01716</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-77.09765</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-12.02103</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-77.09283000000001</v>
-      </c>
-      <c r="I86" t="n">
-        <v>221</v>
-      </c>
-      <c r="J86" t="n">
-        <v>15</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-12.02103</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-77.09283</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>ENMANUEL</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-11.998</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-77.12130999999999</v>
-      </c>
-      <c r="I87" t="n">
-        <v>209</v>
-      </c>
-      <c r="J87" t="n">
-        <v>14</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-11.998</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-77.12131</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>SAN JOSE HERMANOS MARISTAS</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-12.05654</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-77.12863</v>
-      </c>
-      <c r="I88" t="n">
-        <v>852</v>
-      </c>
-      <c r="J88" t="n">
-        <v>56</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-12.05654</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-77.12863</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>BEATA ANA MARIA JAVOUHEY</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-12.03284</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-77.09672</v>
-      </c>
-      <c r="I89" t="n">
-        <v>393</v>
-      </c>
-      <c r="J89" t="n">
-        <v>50</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-12.03284</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-77.09672</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5097,20 +5965,30 @@
           <t>JUANITO BOSCO</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>-12.02437</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-77.13332</v>
-      </c>
-      <c r="I90" t="n">
-        <v>446</v>
-      </c>
-      <c r="J90" t="n">
-        <v>36</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-12.02437</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-77.13332</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5149,20 +6027,30 @@
           <t>MARIA REINA DE CORAZONES</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>-12.04606</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-77.11013</v>
-      </c>
-      <c r="I91" t="n">
-        <v>397</v>
-      </c>
-      <c r="J91" t="n">
-        <v>19</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-12.04606</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-77.11013</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5201,20 +6089,30 @@
           <t>VIRGEN DE CHAPI</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>-12.00975</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-77.10239</v>
-      </c>
-      <c r="I92" t="n">
-        <v>347</v>
-      </c>
-      <c r="J92" t="n">
-        <v>25</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-12.00975</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-77.10239</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -5253,20 +6151,30 @@
           <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
-      <c r="G93" t="n">
-        <v>-11.93995</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-77.13217</v>
-      </c>
-      <c r="I93" t="n">
-        <v>346</v>
-      </c>
-      <c r="J93" t="n">
-        <v>25</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-11.93995</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-77.13217</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5305,20 +6213,30 @@
           <t>COPRODELI AGUSTIN HIPONA</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>-12.02325</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-77.13486399999999</v>
-      </c>
-      <c r="I94" t="n">
-        <v>645</v>
-      </c>
-      <c r="J94" t="n">
-        <v>30</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-12.02325</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-77.134864</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5357,20 +6275,30 @@
           <t>ALBORADA</t>
         </is>
       </c>
-      <c r="G95" t="n">
-        <v>-12.05911</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-77.13352999999999</v>
-      </c>
-      <c r="I95" t="n">
-        <v>209</v>
-      </c>
-      <c r="J95" t="n">
-        <v>19</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-12.05911</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-77.13353</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5409,20 +6337,30 @@
           <t>JESUS SALVADOR</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>-12.0023</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-77.10136</v>
-      </c>
-      <c r="I96" t="n">
-        <v>206</v>
-      </c>
-      <c r="J96" t="n">
-        <v>22</v>
-      </c>
-      <c r="K96" t="n">
-        <v>1</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-12.0023</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-77.10136</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5461,20 +6399,30 @@
           <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G97" t="n">
-        <v>-12.0582</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-77.13813</v>
-      </c>
-      <c r="I97" t="n">
-        <v>305</v>
-      </c>
-      <c r="J97" t="n">
-        <v>22</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-12.0582</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-77.13813</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5513,20 +6461,30 @@
           <t>ALFREDO REBAZA ACOSTA DE LOS JAZMINES</t>
         </is>
       </c>
-      <c r="G98" t="n">
-        <v>-12.00359</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-77.10818</v>
-      </c>
-      <c r="I98" t="n">
-        <v>1215</v>
-      </c>
-      <c r="J98" t="n">
-        <v>40</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-12.00359</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-77.10818</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5565,20 +6523,30 @@
           <t>COPRODELI SAN VICENTE</t>
         </is>
       </c>
-      <c r="G99" t="n">
-        <v>-12.01274</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-77.13646</v>
-      </c>
-      <c r="I99" t="n">
-        <v>359</v>
-      </c>
-      <c r="J99" t="n">
-        <v>13</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-12.01274</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-77.13646</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5617,20 +6585,30 @@
           <t>BERTOLT BRECHT</t>
         </is>
       </c>
-      <c r="G100" t="n">
-        <v>-12.04986</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-77.07886999999999</v>
-      </c>
-      <c r="I100" t="n">
-        <v>1151</v>
-      </c>
-      <c r="J100" t="n">
-        <v>81</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-12.04986</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-77.07887</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1151</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5669,20 +6647,30 @@
           <t>MI JESUS</t>
         </is>
       </c>
-      <c r="G101" t="n">
-        <v>-12.04966</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-77.10399</v>
-      </c>
-      <c r="I101" t="n">
-        <v>14</v>
-      </c>
-      <c r="J101" t="n">
-        <v>3</v>
-      </c>
-      <c r="K101" t="n">
-        <v>1</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-12.04966</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-77.10399</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5721,20 +6709,30 @@
           <t>LIBERTADOR SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G102" t="n">
-        <v>-12.06242</v>
-      </c>
-      <c r="H102" t="n">
-        <v>-77.14131</v>
-      </c>
-      <c r="I102" t="n">
-        <v>228</v>
-      </c>
-      <c r="J102" t="n">
-        <v>11</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-12.06242</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-77.14131</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5773,20 +6771,30 @@
           <t>EL NIÑO DOCTORCITO</t>
         </is>
       </c>
-      <c r="G103" t="n">
-        <v>-12.02372</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-77.09820999999999</v>
-      </c>
-      <c r="I103" t="n">
-        <v>162</v>
-      </c>
-      <c r="J103" t="n">
-        <v>8</v>
-      </c>
-      <c r="K103" t="n">
-        <v>2</v>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-12.02372</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-77.09821</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5825,20 +6833,30 @@
           <t>EL MUNDO DE LOS NIÑOS</t>
         </is>
       </c>
-      <c r="G104" t="n">
-        <v>-11.99594</v>
-      </c>
-      <c r="H104" t="n">
-        <v>-77.12035</v>
-      </c>
-      <c r="I104" t="n">
-        <v>242</v>
-      </c>
-      <c r="J104" t="n">
-        <v>18</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-11.99594</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-77.12035</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5877,20 +6895,30 @@
           <t>ANGELES DE FATIMA</t>
         </is>
       </c>
-      <c r="G105" t="n">
-        <v>-12.055242</v>
-      </c>
-      <c r="H105" t="n">
-        <v>-77.10754799999999</v>
-      </c>
-      <c r="I105" t="n">
-        <v>102</v>
-      </c>
-      <c r="J105" t="n">
-        <v>8</v>
-      </c>
-      <c r="K105" t="n">
-        <v>1</v>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-12.055242</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-77.107548</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5929,20 +6957,30 @@
           <t>ESCUELA DEL BUEN SABER</t>
         </is>
       </c>
-      <c r="G106" t="n">
-        <v>-11.9976</v>
-      </c>
-      <c r="H106" t="n">
-        <v>-77.10809999999999</v>
-      </c>
-      <c r="I106" t="n">
-        <v>204</v>
-      </c>
-      <c r="J106" t="n">
-        <v>11</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-11.9976</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-77.1081</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5981,20 +7019,30 @@
           <t>TRILCE CALLAO</t>
         </is>
       </c>
-      <c r="G107" t="n">
-        <v>-12.05939</v>
-      </c>
-      <c r="H107" t="n">
-        <v>-77.13290000000001</v>
-      </c>
-      <c r="I107" t="n">
-        <v>418</v>
-      </c>
-      <c r="J107" t="n">
-        <v>44</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-12.05939</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-77.1329</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -6033,20 +7081,30 @@
           <t>LUIS ENRIQUE X</t>
         </is>
       </c>
-      <c r="G108" t="n">
-        <v>-12.035485</v>
-      </c>
-      <c r="H108" t="n">
-        <v>-77.095162</v>
-      </c>
-      <c r="I108" t="n">
-        <v>238</v>
-      </c>
-      <c r="J108" t="n">
-        <v>14</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-12.035485</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-77.095162</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -6085,20 +7143,30 @@
           <t>SAN LUIS GONZAGA</t>
         </is>
       </c>
-      <c r="G109" t="n">
-        <v>-12.01823</v>
-      </c>
-      <c r="H109" t="n">
-        <v>-77.09402</v>
-      </c>
-      <c r="I109" t="n">
-        <v>436</v>
-      </c>
-      <c r="J109" t="n">
-        <v>20</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-12.01823</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-77.09402</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -6137,20 +7205,30 @@
           <t>SACO OLIVEROS APEIRON</t>
         </is>
       </c>
-      <c r="G110" t="n">
-        <v>-12.026927</v>
-      </c>
-      <c r="H110" t="n">
-        <v>-77.093075</v>
-      </c>
-      <c r="I110" t="n">
-        <v>1535</v>
-      </c>
-      <c r="J110" t="n">
-        <v>49</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-12.026927</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-77.093075</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -6189,20 +7267,30 @@
           <t>ANGELES DE FATIMA SECUNDARIA</t>
         </is>
       </c>
-      <c r="G111" t="n">
-        <v>-12.05482</v>
-      </c>
-      <c r="H111" t="n">
-        <v>-77.10704</v>
-      </c>
-      <c r="I111" t="n">
-        <v>129</v>
-      </c>
-      <c r="J111" t="n">
-        <v>5</v>
-      </c>
-      <c r="K111" t="n">
-        <v>1</v>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-12.05482</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-77.10704</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -6241,20 +7329,30 @@
           <t>137 FEDERICO VILLARREAL</t>
         </is>
       </c>
-      <c r="G112" t="n">
-        <v>-11.9786</v>
-      </c>
-      <c r="H112" t="n">
-        <v>-77.11969999999999</v>
-      </c>
-      <c r="I112" t="n">
-        <v>208</v>
-      </c>
-      <c r="J112" t="n">
-        <v>11</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-11.9786</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-77.1197</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -6293,20 +7391,30 @@
           <t>JESUS ES MI LUZ</t>
         </is>
       </c>
-      <c r="G113" t="n">
-        <v>-12.0558</v>
-      </c>
-      <c r="H113" t="n">
-        <v>-77.11271000000001</v>
-      </c>
-      <c r="I113" t="n">
-        <v>334</v>
-      </c>
-      <c r="J113" t="n">
-        <v>20</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-12.0558</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-77.11271</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -6345,20 +7453,30 @@
           <t>AMADEUS MOZART DE OQUENDO</t>
         </is>
       </c>
-      <c r="G114" t="n">
-        <v>-11.98065</v>
-      </c>
-      <c r="H114" t="n">
-        <v>-77.11527</v>
-      </c>
-      <c r="I114" t="n">
-        <v>460</v>
-      </c>
-      <c r="J114" t="n">
-        <v>17</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-11.98065</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-77.11527</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -6397,20 +7515,30 @@
           <t>SAN AGUSTIN DE LOS SAIRES</t>
         </is>
       </c>
-      <c r="G115" t="n">
-        <v>-11.967735</v>
-      </c>
-      <c r="H115" t="n">
-        <v>-77.123003</v>
-      </c>
-      <c r="I115" t="n">
-        <v>448</v>
-      </c>
-      <c r="J115" t="n">
-        <v>27</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0</v>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-11.967735</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-77.123003</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6449,20 +7577,30 @@
           <t>BELLA UNION II</t>
         </is>
       </c>
-      <c r="G116" t="n">
-        <v>-12.04617</v>
-      </c>
-      <c r="H116" t="n">
-        <v>-77.11360000000001</v>
-      </c>
-      <c r="I116" t="n">
-        <v>453</v>
-      </c>
-      <c r="J116" t="n">
-        <v>17</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-12.04617</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-77.1136</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -6501,20 +7639,30 @@
           <t>MARIA REINA DE LA ESPERANZA</t>
         </is>
       </c>
-      <c r="G117" t="n">
-        <v>-12.0022</v>
-      </c>
-      <c r="H117" t="n">
-        <v>-77.10862</v>
-      </c>
-      <c r="I117" t="n">
-        <v>559</v>
-      </c>
-      <c r="J117" t="n">
-        <v>27</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0</v>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-12.0022</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-77.10862</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -6553,20 +7701,30 @@
           <t>3090 FRANCO PERUANO</t>
         </is>
       </c>
-      <c r="G118" t="n">
-        <v>-12.0318</v>
-      </c>
-      <c r="H118" t="n">
-        <v>-77.0979</v>
-      </c>
-      <c r="I118" t="n">
-        <v>567</v>
-      </c>
-      <c r="J118" t="n">
-        <v>26</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-12.0318</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-77.0979</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -6605,20 +7763,30 @@
           <t>COPRODELI SAN MIGUEL</t>
         </is>
       </c>
-      <c r="G119" t="n">
-        <v>-12.02069</v>
-      </c>
-      <c r="H119" t="n">
-        <v>-77.13847</v>
-      </c>
-      <c r="I119" t="n">
-        <v>601</v>
-      </c>
-      <c r="J119" t="n">
-        <v>31</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0</v>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-12.02069</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-77.13847</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -6657,20 +7825,30 @@
           <t>2093 SANTA ROSA</t>
         </is>
       </c>
-      <c r="G120" t="n">
-        <v>-11.989659</v>
-      </c>
-      <c r="H120" t="n">
-        <v>-77.117276</v>
-      </c>
-      <c r="I120" t="n">
-        <v>600</v>
-      </c>
-      <c r="J120" t="n">
-        <v>30</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-11.989659</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-77.117276</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -6709,20 +7887,30 @@
           <t>5136 FERNANDO BELAUNDE TERRY</t>
         </is>
       </c>
-      <c r="G121" t="n">
-        <v>-12.01088</v>
-      </c>
-      <c r="H121" t="n">
-        <v>-77.1358</v>
-      </c>
-      <c r="I121" t="n">
-        <v>478</v>
-      </c>
-      <c r="J121" t="n">
-        <v>25</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-12.01088</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-77.1358</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -6761,20 +7949,30 @@
           <t>5126</t>
         </is>
       </c>
-      <c r="G122" t="n">
-        <v>-12.00561</v>
-      </c>
-      <c r="H122" t="n">
-        <v>-77.10623</v>
-      </c>
-      <c r="I122" t="n">
-        <v>723</v>
-      </c>
-      <c r="J122" t="n">
-        <v>12</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-12.00561</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-77.10623</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -6813,20 +8011,30 @@
           <t>MI DIVINO NIÑO JESUS GUADALUPANO</t>
         </is>
       </c>
-      <c r="G123" t="n">
-        <v>-12.04296</v>
-      </c>
-      <c r="H123" t="n">
-        <v>-77.11915</v>
-      </c>
-      <c r="I123" t="n">
-        <v>86</v>
-      </c>
-      <c r="J123" t="n">
-        <v>9</v>
-      </c>
-      <c r="K123" t="n">
-        <v>1</v>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-12.04296</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-77.11915</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -6865,20 +8073,30 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="G124" t="n">
-        <v>-12.06395</v>
-      </c>
-      <c r="H124" t="n">
-        <v>-77.13942</v>
-      </c>
-      <c r="I124" t="n">
-        <v>32</v>
-      </c>
-      <c r="J124" t="n">
-        <v>3</v>
-      </c>
-      <c r="K124" t="n">
-        <v>1</v>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-12.06395</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-77.13942</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -6917,20 +8135,30 @@
           <t>SOR MARIA ROSA DE JESUS</t>
         </is>
       </c>
-      <c r="G125" t="n">
-        <v>-12.06397</v>
-      </c>
-      <c r="H125" t="n">
-        <v>-77.13956</v>
-      </c>
-      <c r="I125" t="n">
-        <v>31</v>
-      </c>
-      <c r="J125" t="n">
-        <v>3</v>
-      </c>
-      <c r="K125" t="n">
-        <v>1</v>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-12.06397</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-77.13956</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -6969,20 +8197,30 @@
           <t>SAN AGUSTIN DE OQUENDO</t>
         </is>
       </c>
-      <c r="G126" t="n">
-        <v>-11.97002</v>
-      </c>
-      <c r="H126" t="n">
-        <v>-77.12221</v>
-      </c>
-      <c r="I126" t="n">
-        <v>471</v>
-      </c>
-      <c r="J126" t="n">
-        <v>23</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-11.97002</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-77.12221</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -7021,20 +8259,30 @@
           <t>INGENIERIA OQUENDO</t>
         </is>
       </c>
-      <c r="G127" t="n">
-        <v>-11.97686</v>
-      </c>
-      <c r="H127" t="n">
-        <v>-77.11505</v>
-      </c>
-      <c r="I127" t="n">
-        <v>233</v>
-      </c>
-      <c r="J127" t="n">
-        <v>18</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0</v>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-11.97686</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-77.11505</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -7073,20 +8321,30 @@
           <t>FRANCISCO DE ZELA</t>
         </is>
       </c>
-      <c r="G128" t="n">
-        <v>-12.01256</v>
-      </c>
-      <c r="H128" t="n">
-        <v>-77.09765</v>
-      </c>
-      <c r="I128" t="n">
-        <v>277</v>
-      </c>
-      <c r="J128" t="n">
-        <v>20</v>
-      </c>
-      <c r="K128" t="n">
-        <v>1</v>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-12.01256</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-77.09765</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -7125,20 +8383,30 @@
           <t>CRISTIANO EMANUEL</t>
         </is>
       </c>
-      <c r="G129" t="n">
-        <v>-12.02556</v>
-      </c>
-      <c r="H129" t="n">
-        <v>-77.1339</v>
-      </c>
-      <c r="I129" t="n">
-        <v>304</v>
-      </c>
-      <c r="J129" t="n">
-        <v>23</v>
-      </c>
-      <c r="K129" t="n">
-        <v>0</v>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-12.02556</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-77.1339</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -7177,20 +8445,30 @@
           <t>5139 LAS COLINAS</t>
         </is>
       </c>
-      <c r="G130" t="n">
-        <v>-12.00322</v>
-      </c>
-      <c r="H130" t="n">
-        <v>-77.1015</v>
-      </c>
-      <c r="I130" t="n">
-        <v>694</v>
-      </c>
-      <c r="J130" t="n">
-        <v>34</v>
-      </c>
-      <c r="K130" t="n">
-        <v>0</v>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-12.00322</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-77.1015</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -7229,20 +8507,30 @@
           <t>SAN JUAN EL BAUTISTA</t>
         </is>
       </c>
-      <c r="G131" t="n">
-        <v>-11.94282</v>
-      </c>
-      <c r="H131" t="n">
-        <v>-77.13539</v>
-      </c>
-      <c r="I131" t="n">
-        <v>674</v>
-      </c>
-      <c r="J131" t="n">
-        <v>41</v>
-      </c>
-      <c r="K131" t="n">
-        <v>0</v>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-11.94282</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-77.13539</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -7281,20 +8569,30 @@
           <t>COPRODELI MONSEÑOR RICARDO DURAND</t>
         </is>
       </c>
-      <c r="G132" t="n">
-        <v>-11.996618</v>
-      </c>
-      <c r="H132" t="n">
-        <v>-77.123783</v>
-      </c>
-      <c r="I132" t="n">
-        <v>279</v>
-      </c>
-      <c r="J132" t="n">
-        <v>11</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0</v>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-11.996618</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-77.123783</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -7333,20 +8631,30 @@
           <t>BLAS PASCAL</t>
         </is>
       </c>
-      <c r="G133" t="n">
-        <v>-11.97584</v>
-      </c>
-      <c r="H133" t="n">
-        <v>-77.11408</v>
-      </c>
-      <c r="I133" t="n">
-        <v>816</v>
-      </c>
-      <c r="J133" t="n">
-        <v>50</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0</v>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-11.97584</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-77.11408</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -7385,20 +8693,30 @@
           <t>MATER PURISSIMA</t>
         </is>
       </c>
-      <c r="G134" t="n">
-        <v>-12.06235</v>
-      </c>
-      <c r="H134" t="n">
-        <v>-77.14369000000001</v>
-      </c>
-      <c r="I134" t="n">
-        <v>190</v>
-      </c>
-      <c r="J134" t="n">
-        <v>18</v>
-      </c>
-      <c r="K134" t="n">
-        <v>1</v>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-12.06235</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-77.14369</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -7437,20 +8755,30 @@
           <t>INTELLECTUM SANTA ISABEL</t>
         </is>
       </c>
-      <c r="G135" t="n">
-        <v>-12.051671</v>
-      </c>
-      <c r="H135" t="n">
-        <v>-77.11158500000001</v>
-      </c>
-      <c r="I135" t="n">
-        <v>353</v>
-      </c>
-      <c r="J135" t="n">
-        <v>25</v>
-      </c>
-      <c r="K135" t="n">
-        <v>0</v>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-12.051671</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-77.111585</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -7489,20 +8817,30 @@
           <t>SAGRADO NIÑO JESUS CHAPERITO</t>
         </is>
       </c>
-      <c r="G136" t="n">
-        <v>-11.97775</v>
-      </c>
-      <c r="H136" t="n">
-        <v>-77.11459000000001</v>
-      </c>
-      <c r="I136" t="n">
-        <v>234</v>
-      </c>
-      <c r="J136" t="n">
-        <v>29</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0</v>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-11.97775</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-77.11459</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -7541,20 +8879,30 @@
           <t>MARIA REINA DE CORAZONES</t>
         </is>
       </c>
-      <c r="G137" t="n">
-        <v>-12.03402</v>
-      </c>
-      <c r="H137" t="n">
-        <v>-77.09815</v>
-      </c>
-      <c r="I137" t="n">
-        <v>484</v>
-      </c>
-      <c r="J137" t="n">
-        <v>25</v>
-      </c>
-      <c r="K137" t="n">
-        <v>0</v>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-12.03402</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-77.09815</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -7593,20 +8941,30 @@
           <t>SAINT MARIA MAGDALENA' S KINDER</t>
         </is>
       </c>
-      <c r="G138" t="n">
-        <v>-12.01739</v>
-      </c>
-      <c r="H138" t="n">
-        <v>-77.09376</v>
-      </c>
-      <c r="I138" t="n">
-        <v>22</v>
-      </c>
-      <c r="J138" t="n">
-        <v>4</v>
-      </c>
-      <c r="K138" t="n">
-        <v>1</v>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-12.01739</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-77.09376</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -7645,20 +9003,30 @@
           <t>SAN BENITO DE OQUENDO S.A.C.</t>
         </is>
       </c>
-      <c r="G139" t="n">
-        <v>-11.977969</v>
-      </c>
-      <c r="H139" t="n">
-        <v>-77.122927</v>
-      </c>
-      <c r="I139" t="n">
-        <v>690</v>
-      </c>
-      <c r="J139" t="n">
-        <v>31</v>
-      </c>
-      <c r="K139" t="n">
-        <v>0</v>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-11.977969</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-77.122927</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -7697,20 +9065,30 @@
           <t>NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
-      <c r="G140" t="n">
-        <v>-11.98632</v>
-      </c>
-      <c r="H140" t="n">
-        <v>-77.12007</v>
-      </c>
-      <c r="I140" t="n">
-        <v>269</v>
-      </c>
-      <c r="J140" t="n">
-        <v>13</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0</v>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-11.98632</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-77.12007</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -7749,20 +9127,30 @@
           <t>TALENTUS SCHOOL</t>
         </is>
       </c>
-      <c r="G141" t="n">
-        <v>-12.00635</v>
-      </c>
-      <c r="H141" t="n">
-        <v>-77.10346</v>
-      </c>
-      <c r="I141" t="n">
-        <v>603</v>
-      </c>
-      <c r="J141" t="n">
-        <v>12</v>
-      </c>
-      <c r="K141" t="n">
-        <v>0</v>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-12.00635</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-77.10346</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -7801,20 +9189,30 @@
           <t>82 PASTORCITOS DE OQUENDO</t>
         </is>
       </c>
-      <c r="G142" t="n">
-        <v>-11.9779</v>
-      </c>
-      <c r="H142" t="n">
-        <v>-77.12332000000001</v>
-      </c>
-      <c r="I142" t="n">
-        <v>209</v>
-      </c>
-      <c r="J142" t="n">
-        <v>9</v>
-      </c>
-      <c r="K142" t="n">
-        <v>0</v>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-11.9779</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-77.12332</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -7853,20 +9251,30 @@
           <t>MARILLAC SCHOOL</t>
         </is>
       </c>
-      <c r="G143" t="n">
-        <v>-12.01791</v>
-      </c>
-      <c r="H143" t="n">
-        <v>-77.09319000000001</v>
-      </c>
-      <c r="I143" t="n">
-        <v>35</v>
-      </c>
-      <c r="J143" t="n">
-        <v>4</v>
-      </c>
-      <c r="K143" t="n">
-        <v>1</v>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-12.01791</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-77.09319</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -7905,20 +9313,30 @@
           <t>INNOVA SCHOOLS - CALLAO LEMOS</t>
         </is>
       </c>
-      <c r="G144" t="n">
-        <v>-12.04917</v>
-      </c>
-      <c r="H144" t="n">
-        <v>-77.09473</v>
-      </c>
-      <c r="I144" t="n">
-        <v>962</v>
-      </c>
-      <c r="J144" t="n">
-        <v>48</v>
-      </c>
-      <c r="K144" t="n">
-        <v>0</v>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-12.04917</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-77.09473</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -7957,20 +9375,30 @@
           <t>5155 BICENTENARIO LAS DELICIAS DE OQUENDO</t>
         </is>
       </c>
-      <c r="G145" t="n">
-        <v>-11.98181</v>
-      </c>
-      <c r="H145" t="n">
-        <v>-77.11578</v>
-      </c>
-      <c r="I145" t="n">
-        <v>395</v>
-      </c>
-      <c r="J145" t="n">
-        <v>16</v>
-      </c>
-      <c r="K145" t="n">
-        <v>0</v>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-11.98181</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-77.11578</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -8009,20 +9437,30 @@
           <t>DIEGO THOMSON</t>
         </is>
       </c>
-      <c r="G146" t="n">
-        <v>-12.05859</v>
-      </c>
-      <c r="H146" t="n">
-        <v>-77.13059</v>
-      </c>
-      <c r="I146" t="n">
-        <v>278</v>
-      </c>
-      <c r="J146" t="n">
-        <v>21</v>
-      </c>
-      <c r="K146" t="n">
-        <v>0</v>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-12.05859</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-77.13059</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -8061,20 +9499,30 @@
           <t>STAR TALENT PERU SCHOOL</t>
         </is>
       </c>
-      <c r="G147" t="n">
-        <v>-12.017783</v>
-      </c>
-      <c r="H147" t="n">
-        <v>-77.09138</v>
-      </c>
-      <c r="I147" t="n">
-        <v>252</v>
-      </c>
-      <c r="J147" t="n">
-        <v>28</v>
-      </c>
-      <c r="K147" t="n">
-        <v>0</v>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-12.017783</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-77.09138</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -8113,20 +9561,30 @@
           <t>INNOVA SCHOOLS - CALLAO SANTA ROSA</t>
         </is>
       </c>
-      <c r="G148" t="n">
-        <v>-12.01167</v>
-      </c>
-      <c r="H148" t="n">
-        <v>-77.10567</v>
-      </c>
-      <c r="I148" t="n">
-        <v>1147</v>
-      </c>
-      <c r="J148" t="n">
-        <v>51</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0</v>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-12.01167</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-77.10567</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -8165,20 +9623,30 @@
           <t>UNIVERSIA DEL CALLAO</t>
         </is>
       </c>
-      <c r="G149" t="n">
-        <v>-12.00607</v>
-      </c>
-      <c r="H149" t="n">
-        <v>-77.09687</v>
-      </c>
-      <c r="I149" t="n">
-        <v>360</v>
-      </c>
-      <c r="J149" t="n">
-        <v>19</v>
-      </c>
-      <c r="K149" t="n">
-        <v>0</v>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-12.00607</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-77.09687</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -8217,20 +9685,30 @@
           <t>AVE MARIA</t>
         </is>
       </c>
-      <c r="G150" t="n">
-        <v>-12.06174</v>
-      </c>
-      <c r="H150" t="n">
-        <v>-77.13508</v>
-      </c>
-      <c r="I150" t="n">
-        <v>83</v>
-      </c>
-      <c r="J150" t="n">
-        <v>5</v>
-      </c>
-      <c r="K150" t="n">
-        <v>1</v>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-12.06174</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-77.13508</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -8269,20 +9747,30 @@
           <t>PAEBA PILOTO REGIONAL DE EXCELENCIA</t>
         </is>
       </c>
-      <c r="G151" t="n">
-        <v>-11.93978</v>
-      </c>
-      <c r="H151" t="n">
-        <v>-77.13185</v>
-      </c>
-      <c r="I151" t="n">
-        <v>0</v>
-      </c>
-      <c r="J151" t="n">
-        <v>0</v>
-      </c>
-      <c r="K151" t="n">
-        <v>0</v>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-11.93978</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-77.13185</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/CALLAO-CALLAO-CALLAO.xlsx
+++ b/ZonasEscolares/excels/CALLAO-CALLAO-CALLAO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>139375</t>
+          <t>140350</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>62 PASITOS DE JESUS</t>
+          <t>PAEBA PILOTO REGIONAL DE EXCELENCIA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.05516</t>
+          <t>-11.93978</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.13472</t>
+          <t>-77.13185</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>139380</t>
+          <t>139728</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>64 DIVINO NIÑO JESUS</t>
+          <t>109 DIVINO JESUS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.05287</t>
+          <t>-12.02312</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.13031</t>
+          <t>-77.09538</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>139403</t>
+          <t>139851</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>92 LOS NIÑITOS DE SANTA ROSA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.0218</t>
+          <t>-12.05338</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.1368</t>
+          <t>-77.1198</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>139422</t>
+          <t>139441</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69 MARIA AUXILIADORA</t>
+          <t>073 SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.03731</t>
+          <t>-12.01661</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.09664</t>
+          <t>-77.09039</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>268</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,27 +811,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>139441</t>
+          <t>139484</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>073 SEÑOR DE LA MISERICORDIA</t>
+          <t>78 AMIGUITOS DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.01661</t>
+          <t>-12.03371</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.09039</t>
+          <t>-77.09884</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>239</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>139455</t>
+          <t>139506</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>76 MI AMIGO JESUS</t>
+          <t>80 LOS NIÑOS DE JESUS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.04083</t>
+          <t>-11.99643</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.12267</t>
+          <t>-77.1244</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>260</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>139460</t>
+          <t>139714</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>77 SANTISIMA VIRGEN DEL CARMEN</t>
+          <t>100 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.01001</t>
+          <t>-12.00085</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.10459</t>
+          <t>-77.10856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>249</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>139479</t>
+          <t>140147</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JUAN INGUNZA VALDIVIA</t>
+          <t>5078 JOSE A. QUIÑONES GONZALES</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.01202</t>
+          <t>-12.0528</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.0979</t>
+          <t>-77.12218</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>232</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,27 +1059,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>139484</t>
+          <t>142212</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>78 AMIGUITOS DE SAN MARTIN</t>
+          <t>LIBERTADOR SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.03371</t>
+          <t>-12.06242</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.09884</t>
+          <t>-77.14131</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>228</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1121,27 +1121,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>139506</t>
+          <t>171822</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>80 LOS NIÑOS DE JESUS</t>
+          <t>ESCUELA DEL BUEN SABER</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.99643</t>
+          <t>-11.9976</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.1244</t>
+          <t>-77.1081</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>139511</t>
+          <t>553171</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4008 NUESTRA SEÑORA DE FATIMA</t>
+          <t>137 FEDERICO VILLARREAL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.05278</t>
+          <t>-11.9786</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.10824</t>
+          <t>-77.1197</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>208</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>139587</t>
+          <t>595883</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>94 MIGUEL GRAU</t>
+          <t>COPRODELI MONSEÑOR RICARDO DURAND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.04614</t>
+          <t>-11.996618</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.10393</t>
+          <t>-77.123783</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>279</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>139605</t>
+          <t>140091</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>84 NIÑA MARIA</t>
+          <t>5076 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.0159</t>
+          <t>-11.9433</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.10013</t>
+          <t>-77.1326</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>139610</t>
+          <t>139422</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>85 NIÑO JESUS</t>
+          <t>69 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.01256</t>
+          <t>-12.03731</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.10178</t>
+          <t>-77.09664</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>139629</t>
+          <t>139733</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>86 SEÑOR DE LOS MILAGROS</t>
+          <t>111 MI PEQUEÑO PARAISO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.01318</t>
+          <t>-12.02819</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.10303</t>
+          <t>-77.09627</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>298</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>139634</t>
+          <t>139752</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>87 SANTA ROSA</t>
+          <t>115 VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.01653</t>
+          <t>-12.02384</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.1014</t>
+          <t>-77.09334</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>279</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>139648</t>
+          <t>140388</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5023 ABELARDO GAMARRA</t>
+          <t>98 NIÑITO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.05689</t>
+          <t>-11.94224</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.12657</t>
+          <t>-77.13399</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>310</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>139714</t>
+          <t>594464</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>100 VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.00085</t>
+          <t>-12.00561</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.10856</t>
+          <t>-77.10623</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>723</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>139728</t>
+          <t>748391</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>109 DIVINO JESUS</t>
+          <t>TALENTUS SCHOOL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.02312</t>
+          <t>-12.00635</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.09538</t>
+          <t>-77.10346</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>603</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>139733</t>
+          <t>139380</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>111 MI PEQUEÑO PARAISO</t>
+          <t>64 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.02819</t>
+          <t>-12.05287</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.09627</t>
+          <t>-77.13031</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>301</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>139747</t>
+          <t>139455</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>112 MEDALLITA MILAGROSA</t>
+          <t>76 MI AMIGO JESUS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.99638</t>
+          <t>-12.04083</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.11823</t>
+          <t>-77.12267</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>331</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>139752</t>
+          <t>139460</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>115 VIRGEN DE GUADALUPE</t>
+          <t>77 SANTISIMA VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.02384</t>
+          <t>-12.01001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.09334</t>
+          <t>-77.10459</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>271</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,17 +1927,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>139766</t>
+          <t>139587</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>5040 PEDRO RUIZ</t>
+          <t>94 MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.05041</t>
+          <t>-12.04614</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>139785</t>
+          <t>139605</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4001 DOS DE MAYO</t>
+          <t>84 NIÑA MARIA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.06411</t>
+          <t>-12.0159</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.15229</t>
+          <t>-77.10013</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>304</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>139808</t>
+          <t>139610</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4007 VIRGEN DEL PILAR</t>
+          <t>85 NIÑO JESUS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.0549</t>
+          <t>-12.01256</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.11255</t>
+          <t>-77.10178</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>312</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>139827</t>
+          <t>139634</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>5032 ENRIQUE DEL HORME</t>
+          <t>87 SANTA ROSA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.05201</t>
+          <t>-12.01653</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.10136</t>
+          <t>-77.1014</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>139832</t>
+          <t>141811</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5001 LUISA DE SABOGAL</t>
+          <t>COPRODELI SAN VICENTE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.06053</t>
+          <t>-12.01274</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.14445</t>
+          <t>-77.13646</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>359</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>139846</t>
+          <t>722334</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4006 SANTA ROSA DE AMERICA</t>
+          <t>NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.05609</t>
+          <t>-11.98632</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.11615</t>
+          <t>-77.12007</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>269</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,37 +2299,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>139851</t>
+          <t>140190</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>92 LOS NIÑITOS DE SANTA ROSA</t>
+          <t>5080 SOR ANA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.05338</t>
+          <t>-12.01107</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.1198</t>
+          <t>-77.10339</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>134</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>139870</t>
+          <t>140883</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>5031 CESAR VALLEJO</t>
+          <t>JORDAN DE JESUS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.04287</t>
+          <t>-11.99636</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.10235</t>
+          <t>-77.12294</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>219</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2485,37 +2485,37 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>139889</t>
+          <t>140920</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>5019 AUGUSTO CAZORLA</t>
+          <t>ENMANUEL</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.05306</t>
+          <t>-11.998</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.13395</t>
+          <t>-77.12131</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>139894</t>
+          <t>332877</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>5024 FRANCISCO MIRO QUESADA CANTUARIAS</t>
+          <t>LUIS ENRIQUE X</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.05389</t>
+          <t>-12.035485</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.12877</t>
+          <t>-77.095162</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>139907</t>
+          <t>139629</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>REPUBLICA DE VENEZUELA</t>
+          <t>86 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.05177</t>
+          <t>-12.01318</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.13086</t>
+          <t>-77.10303</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>336</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>139912</t>
+          <t>139950</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4010 HERMANOS RAFAEL SAMUEL Y EMILIO MOISES GOMEZ PAQUIYAURI</t>
+          <t>5003 VIRGEN DE LA INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.97657</t>
+          <t>-12.06318</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.12293</t>
+          <t>-77.14344</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>306</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>139926</t>
+          <t>139974</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4011 LA TABOADA DE LAS FRESAS</t>
+          <t>5006 ALBERTO SECADA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.00276</t>
+          <t>-12.05868</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.11283</t>
+          <t>-77.14027</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>139931</t>
+          <t>140915</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4016 NESTOR GAMBETA BONATTI</t>
+          <t>CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.0434</t>
+          <t>-12.02103</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.1137</t>
+          <t>-77.09283</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>139945</t>
+          <t>139511</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4018 ABRAHAM VALDELOMAR</t>
+          <t>4008 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.04283</t>
+          <t>-12.05278</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.11144</t>
+          <t>-77.10824</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>428</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>139950</t>
+          <t>139926</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>5003 VIRGEN DE LA INMACULADA CONCEPCION</t>
+          <t>4011 LA TABOADA DE LAS FRESAS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.06318</t>
+          <t>-12.00276</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.14344</t>
+          <t>-77.11283</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>430</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>139969</t>
+          <t>846103</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>5005 GENMO DON JOSE DE SAN MARTIN</t>
+          <t>5155 BICENTENARIO LAS DELICIAS DE OQUENDO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.05954</t>
+          <t>-11.98181</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.13717</t>
+          <t>-77.11578</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>395</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>139974</t>
+          <t>139375</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>5006 ALBERTO SECADA</t>
+          <t>62 PASITOS DE JESUS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.05868</t>
+          <t>-12.05516</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.14027</t>
+          <t>-77.13472</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>339</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>139988</t>
+          <t>140086</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>5007 NUESTRA SEÑORA DE GUADALUPE</t>
+          <t>5010 VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.05276</t>
+          <t>-12.04644</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.1402</t>
+          <t>-77.10265</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>392</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>140005</t>
+          <t>580768</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>5042 JUAN FRANCISCO DE LA BODEGA Y QUADRA</t>
+          <t>AMADEUS MOZART DE OQUENDO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.04569</t>
+          <t>-11.98065</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.11355</t>
+          <t>-77.11527</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>460</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>140010</t>
+          <t>590606</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>5046 JOSE GALVEZ EGUSQUIZA</t>
+          <t>BELLA UNION II</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.04398</t>
+          <t>-12.04617</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.12434</t>
+          <t>-77.1136</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>453</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>140034</t>
+          <t>142453</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>5048 MARISCAL RAMON CASTILLA</t>
+          <t>EL MUNDO DE LOS NIÑOS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.04143</t>
+          <t>-11.99594</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.12345</t>
+          <t>-77.12035</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>140048</t>
+          <t>594987</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>5049 EMMA DETTMANN DE GUTIERREZ</t>
+          <t>INGENIERIA OQUENDO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.05066</t>
+          <t>-11.97686</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.09526</t>
+          <t>-77.11505</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3415,37 +3415,37 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>140053</t>
+          <t>595996</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>5036 RAFAEL BELAUNDE DIEZ CANSECO</t>
+          <t>MATER PURISSIMA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.03769</t>
+          <t>-12.06235</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.09641</t>
+          <t>-77.14369</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>190</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>140067</t>
+          <t>139832</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>5037 ALMIRANTE MIGUEL GRAU</t>
+          <t>5001 LUISA DE SABOGAL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.02282</t>
+          <t>-12.06053</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-77.13738</t>
+          <t>-77.14445</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>403</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>140086</t>
+          <t>141161</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>5010 VIRGEN DE GUADALUPE</t>
+          <t>MARIA REINA DE CORAZONES</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.04644</t>
+          <t>-12.04606</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-77.10265</t>
+          <t>-77.11013</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>397</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>140091</t>
+          <t>141547</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>5076 NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>ALBORADA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-11.9433</t>
+          <t>-12.05911</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-77.1326</t>
+          <t>-77.13353</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>140109</t>
+          <t>861589</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>5075 INCA GARCILASO DE LA VEGA</t>
+          <t>UNIVERSIA DEL CALLAO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.03424</t>
+          <t>-12.00607</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-77.09829</t>
+          <t>-77.09687</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>140114</t>
+          <t>508800</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>5074 ALCIDES SPELUCIN VEGA</t>
+          <t>SAN LUIS GONZAGA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.00959</t>
+          <t>-12.01823</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-77.09624</t>
+          <t>-77.09402</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>436</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>140128</t>
+          <t>567941</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>5033 LAS 200 MILLAS</t>
+          <t>JESUS ES MI LUZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-11.9944</t>
+          <t>-12.0558</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-77.1235</t>
+          <t>-77.11271</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>334</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,37 +3849,37 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>140133</t>
+          <t>595034</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>5026 JOSE MARIA ARGUEDAS</t>
+          <t>FRANCISCO DE ZELA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-12.01984</t>
+          <t>-12.01256</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-77.09149</t>
+          <t>-77.09765</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>277</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>140147</t>
+          <t>139827</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>5078 JOSE A. QUIÑONES GONZALES</t>
+          <t>5032 ENRIQUE DEL HORME</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-12.0528</t>
+          <t>-12.05201</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-77.12218</t>
+          <t>-77.10136</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>425</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>140152</t>
+          <t>140897</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>5079 JORGE CHAVEZ DARNELL</t>
+          <t>FLORENCE NIGHTINGALE</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-12.0174</t>
+          <t>-12.01716</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-77.09675</t>
+          <t>-77.09765</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>327</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>140171</t>
+          <t>851533</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>5082 SARITA COLONIA</t>
+          <t>DIEGO THOMSON</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-12.023593</t>
+          <t>-12.05859</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-77.1332</t>
+          <t>-77.13059</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>278</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,37 +4097,37 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>140185</t>
+          <t>141590</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>5083 SAN MARTIN DE PORRES</t>
+          <t>JESUS SALVADOR</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-12.01038</t>
+          <t>-12.0023</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-77.10504</t>
+          <t>-77.10136</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>140190</t>
+          <t>141613</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>5080 SOR ANA DE LOS ANGELES</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-12.01107</t>
+          <t>-12.0582</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-77.10339</t>
+          <t>-77.13813</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>305</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>140208</t>
+          <t>139808</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>5084 CARLOS PHILLIPS</t>
+          <t>4007 VIRGEN DEL PILAR</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-12.017055</t>
+          <t>-12.0549</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-77.090428</t>
+          <t>-77.11255</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>480</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>140213</t>
+          <t>140109</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>5085 RAMIRO PRIALE PRIALE</t>
+          <t>5075 INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-12.01514</t>
+          <t>-12.03424</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-77.09056</t>
+          <t>-77.09829</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>523</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,42 +4345,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>140227</t>
+          <t>140289</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>5089 VIRGEN MARIA</t>
+          <t>JORGE BASADRE GROHMAN</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-11.99932</t>
+          <t>-12.06236</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-77.10861</t>
+          <t>-77.13567</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>410</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>140232</t>
+          <t>594949</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>5092 SANTA ROSA DE LIMA</t>
+          <t>SAN AGUSTIN DE OQUENDO</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-12.02346</t>
+          <t>-11.97002</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-77.10116</t>
+          <t>-77.12221</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>471</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>140246</t>
+          <t>595072</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>5095 JULIO RAMON RIBEYRO</t>
+          <t>CRISTIANO EMANUEL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-12.0253</t>
+          <t>-12.02556</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-77.0965</t>
+          <t>-77.1339</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>304</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>140251</t>
+          <t>139894</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>5097 SAN JUAN MACIAS</t>
+          <t>5024 FRANCISCO MIRO QUESADA CANTUARIAS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-11.99755</t>
+          <t>-12.05389</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-77.11748</t>
+          <t>-77.12877</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>539</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,37 +4593,37 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>140265</t>
+          <t>140232</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>HEROINAS TOLEDO</t>
+          <t>5092 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-12.06186</t>
+          <t>-12.02346</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-77.13567</t>
+          <t>-77.10116</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>521</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>140270</t>
+          <t>140784</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>POLITECNICO NACIONAL DEL CALLAO</t>
+          <t>SAN BENITO DE PALERMO</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-12.044294</t>
+          <t>-11.99852</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-77.099361</t>
+          <t>-77.11808</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>417</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4717,37 +4717,37 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>140289</t>
+          <t>140816</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>JORGE BASADRE GROHMAN</t>
+          <t>JEAN CALVIN LEFRANC</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-12.06236</t>
+          <t>-12.00717</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-77.13567</t>
+          <t>-77.10353</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>140294</t>
+          <t>139648</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>5099 RICARDO PALMA</t>
+          <t>5023 ABELARDO GAMARRA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-12.02017</t>
+          <t>-12.05689</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-77.09931</t>
+          <t>-77.12657</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>568</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>140388</t>
+          <t>140067</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>98 NIÑITO JESUS DE PRAGA</t>
+          <t>5037 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-11.94224</t>
+          <t>-12.02282</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-77.13399</t>
+          <t>-77.13738</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>534</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>140411</t>
+          <t>140736</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>JUAN LINARES ROJAS</t>
+          <t>MERIDIONAL SANTA ANA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-11.97227</t>
+          <t>-12.04089</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-77.1229</t>
+          <t>-77.1249</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>480</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,37 +4965,37 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>140487</t>
+          <t>140760</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>JOSE GALVEZ</t>
+          <t>JERUSALEN</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-12.05679</t>
+          <t>-12.04123</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-77.13601</t>
+          <t>-77.10048</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>274</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>140500</t>
+          <t>141175</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>JUNIOR CESAR DE LOS RIOS</t>
+          <t>VIRGEN DE CHAPI</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.05347</t>
+          <t>-12.00975</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-77.12979</t>
+          <t>-77.10239</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>347</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>140538</t>
+          <t>141255</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NIÑO JESUS DE PRAGA</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-12.01704</t>
+          <t>-11.93995</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-77.09554</t>
+          <t>-77.13217</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>140576</t>
+          <t>594138</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SANTA CRUZ</t>
+          <t>5136 FERNANDO BELAUNDE TERRY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-12.03214</t>
+          <t>-12.01088</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-77.09748</t>
+          <t>-77.1358</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>478</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>140656</t>
+          <t>608461</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NIÑO JESUS MARISCAL CHAPERITO</t>
+          <t>INTELLECTUM SANTA ISABEL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-12.02095</t>
+          <t>-12.051671</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-77.09563</t>
+          <t>-77.111585</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>140675</t>
+          <t>624791</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>LOS OLIVOS</t>
+          <t>MARIA REINA DE CORAZONES</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-12.02196</t>
+          <t>-12.03402</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-77.09209</t>
+          <t>-77.09815</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>484</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>140736</t>
+          <t>140010</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MERIDIONAL SANTA ANA</t>
+          <t>5046 JOSE GALVEZ EGUSQUIZA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-12.04089</t>
+          <t>-12.04398</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-77.1249</t>
+          <t>-77.12434</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>511</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,37 +5399,37 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>140760</t>
+          <t>593662</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>JERUSALEN</t>
+          <t>3090 FRANCO PERUANO</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-12.04123</t>
+          <t>-12.0318</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-77.10048</t>
+          <t>-77.0979</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>567</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>140784</t>
+          <t>140053</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SAN BENITO DE PALERMO</t>
+          <t>5036 RAFAEL BELAUNDE DIEZ CANSECO</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-11.99852</t>
+          <t>-12.03769</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-77.11808</t>
+          <t>-77.09641</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>664</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>140816</t>
+          <t>140227</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>JEAN CALVIN LEFRANC</t>
+          <t>5089 VIRGEN MARIA</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-12.00717</t>
+          <t>-11.99932</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-77.10353</t>
+          <t>-77.10861</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>722</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>140883</t>
+          <t>580805</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>JORDAN DE JESUS</t>
+          <t>SAN AGUSTIN DE LOS SAIRES</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-11.99636</t>
+          <t>-11.967735</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-77.12294</t>
+          <t>-77.123003</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>448</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>140897</t>
+          <t>593558</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FLORENCE NIGHTINGALE</t>
+          <t>MARIA REINA DE LA ESPERANZA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-12.01716</t>
+          <t>-12.0022</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-77.09765</t>
+          <t>-77.10862</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>559</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>140915</t>
+          <t>139766</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CORAZON DE JESUS</t>
+          <t>5040 PEDRO RUIZ</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-12.02103</t>
+          <t>-12.05041</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-77.09283</t>
+          <t>-77.10393</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>501</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>140920</t>
+          <t>140675</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ENMANUEL</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-11.998</t>
+          <t>-12.02196</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-77.12131</t>
+          <t>-77.09209</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>347</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>141038</t>
+          <t>853886</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SAN JOSE HERMANOS MARISTAS</t>
+          <t>STAR TALENT PERU SCHOOL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-12.05654</t>
+          <t>-12.017783</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-77.12863</t>
+          <t>-77.09138</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>141062</t>
+          <t>140152</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>BEATA ANA MARIA JAVOUHEY</t>
+          <t>5079 JORGE CHAVEZ DARNELL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-12.03284</t>
+          <t>-12.0174</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-77.09672</t>
+          <t>-77.09675</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>626</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>141081</t>
+          <t>140656</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>JUANITO BOSCO</t>
+          <t>NIÑO JESUS MARISCAL CHAPERITO</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-12.02437</t>
+          <t>-12.02095</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-77.13332</t>
+          <t>-77.09563</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>260</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>141161</t>
+          <t>618115</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>MARIA REINA DE CORAZONES</t>
+          <t>SAGRADO NIÑO JESUS CHAPERITO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-12.04606</t>
+          <t>-11.97775</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-77.11013</t>
+          <t>-77.11459</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,37 +6081,37 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>141175</t>
+          <t>142066</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>VIRGEN DE CHAPI</t>
+          <t>MI JESUS</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-12.00975</t>
+          <t>-12.04966</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-77.10239</t>
+          <t>-77.10399</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6143,37 +6143,37 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>141255</t>
+          <t>594727</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>MUNDIAL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-11.93995</t>
+          <t>-12.06395</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-77.13217</t>
+          <t>-77.13942</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6205,37 +6205,37 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>141420</t>
+          <t>594850</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>COPRODELI AGUSTIN HIPONA</t>
+          <t>SOR MARIA ROSA DE JESUS</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-12.02325</t>
+          <t>-12.06397</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-77.134864</t>
+          <t>-77.13956</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>141547</t>
+          <t>139846</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ALBORADA</t>
+          <t>4006 SANTA ROSA DE AMERICA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-12.05911</t>
+          <t>-12.05609</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-77.13353</t>
+          <t>-77.11615</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>608</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,37 +6329,37 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>141590</t>
+          <t>141420</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>JESUS SALVADOR</t>
+          <t>COPRODELI AGUSTIN HIPONA</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-12.0023</t>
+          <t>-12.02325</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-77.10136</t>
+          <t>-77.134864</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>645</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>141613</t>
+          <t>593997</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>2093 SANTA ROSA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-12.0582</t>
+          <t>-11.989659</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-77.13813</t>
+          <t>-77.117276</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>141707</t>
+          <t>140185</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ALFREDO REBAZA ACOSTA DE LOS JAZMINES</t>
+          <t>5083 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-12.00359</t>
+          <t>-12.01038</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-77.10818</t>
+          <t>-77.10504</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>732</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>141811</t>
+          <t>593836</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>COPRODELI SAN VICENTE</t>
+          <t>COPRODELI SAN MIGUEL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-12.01274</t>
+          <t>-12.02069</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-77.13646</t>
+          <t>-77.13847</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>601</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>142009</t>
+          <t>691177</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>BERTOLT BRECHT</t>
+          <t>SAN BENITO DE OQUENDO S.A.C.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-12.04986</t>
+          <t>-11.977969</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-77.07887</t>
+          <t>-77.122927</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>690</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6639,37 +6639,37 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>139969</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MI JESUS</t>
+          <t>5005 GENMO DON JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-12.04966</t>
+          <t>-12.05954</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-77.10399</t>
+          <t>-77.13717</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>723</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>142212</t>
+          <t>595425</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>LIBERTADOR SIMON BOLIVAR</t>
+          <t>5139 LAS COLINAS</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-12.06242</t>
+          <t>-12.00322</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-77.14131</t>
+          <t>-77.1015</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>694</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6763,37 +6763,37 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>142269</t>
+          <t>140294</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>EL NIÑO DOCTORCITO</t>
+          <t>5099 RICARDO PALMA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-12.02372</t>
+          <t>-12.02017</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-77.09821</t>
+          <t>-77.09931</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>687</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6825,32 +6825,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>142453</t>
+          <t>139988</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>EL MUNDO DE LOS NIÑOS</t>
+          <t>5007 NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-11.99594</t>
+          <t>-12.05276</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-77.12035</t>
+          <t>-77.1402</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>592</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6887,37 +6887,37 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>143363</t>
+          <t>140487</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ANGELES DE FATIMA</t>
+          <t>JOSE GALVEZ</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-12.055242</t>
+          <t>-12.05679</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-77.107548</t>
+          <t>-77.13601</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>377</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>171822</t>
+          <t>141081</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ESCUELA DEL BUEN SABER</t>
+          <t>JUANITO BOSCO</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-11.9976</t>
+          <t>-12.02437</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-77.1081</t>
+          <t>-77.13332</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>446</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7011,32 +7011,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>300490</t>
+          <t>139931</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>TRILCE CALLAO</t>
+          <t>4016 NESTOR GAMBETA BONATTI</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-12.05939</t>
+          <t>-12.0434</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-77.1329</t>
+          <t>-77.1137</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>789</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7073,37 +7073,37 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>332877</t>
+          <t>651713</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE X</t>
+          <t>SAINT MARIA MAGDALENA' S KINDER</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-12.035485</t>
+          <t>-12.01739</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-77.095162</t>
+          <t>-77.09376</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7135,42 +7135,42 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>508800</t>
+          <t>833167</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SAN LUIS GONZAGA</t>
+          <t>MARILLAC SCHOOL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-12.01823</t>
+          <t>-12.01791</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-77.09402</t>
+          <t>-77.09319</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7197,32 +7197,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>513788</t>
+          <t>139945</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS APEIRON</t>
+          <t>4018 ABRAHAM VALDELOMAR</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-12.026927</t>
+          <t>-12.04283</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-77.093075</t>
+          <t>-77.11144</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>765</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7259,37 +7259,37 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>516051</t>
+          <t>141707</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>ANGELES DE FATIMA SECUNDARIA</t>
+          <t>ALFREDO REBAZA ACOSTA DE LOS JAZMINES</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-12.05482</t>
+          <t>-12.00359</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>-77.10704</t>
+          <t>-77.10818</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7321,32 +7321,32 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>553171</t>
+          <t>140411</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>137 FEDERICO VILLARREAL</t>
+          <t>JUAN LINARES ROJAS</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-11.9786</t>
+          <t>-11.97227</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-77.1197</t>
+          <t>-77.1229</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>792</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7383,32 +7383,32 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>567941</t>
+          <t>595473</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>JESUS ES MI LUZ</t>
+          <t>SAN JUAN EL BAUTISTA</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-12.0558</t>
+          <t>-11.94282</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-77.11271</t>
+          <t>-77.13539</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>674</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7445,32 +7445,32 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>580768</t>
+          <t>140208</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>AMADEUS MOZART DE OQUENDO</t>
+          <t>5084 CARLOS PHILLIPS</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-11.98065</t>
+          <t>-12.017055</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-77.11527</t>
+          <t>-77.090428</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7507,32 +7507,32 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>580805</t>
+          <t>300490</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN DE LOS SAIRES</t>
+          <t>TRILCE CALLAO</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-11.967735</t>
+          <t>-12.05939</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-77.123003</t>
+          <t>-77.1329</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>418</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7569,32 +7569,32 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>590606</t>
+          <t>140048</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>BELLA UNION II</t>
+          <t>5049 EMMA DETTMANN DE GUTIERREZ</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-12.04617</t>
+          <t>-12.05066</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>-77.1136</t>
+          <t>-77.09526</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>781</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7631,32 +7631,32 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>593558</t>
+          <t>140538</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MARIA REINA DE LA ESPERANZA</t>
+          <t>NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-12.0022</t>
+          <t>-12.01704</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>-77.10862</t>
+          <t>-77.09554</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>821</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7693,37 +7693,37 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>593662</t>
+          <t>140265</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>3090 FRANCO PERUANO</t>
+          <t>HEROINAS TOLEDO</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-12.0318</t>
+          <t>-12.06186</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>-77.0979</t>
+          <t>-77.13567</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>449</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7755,32 +7755,32 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>593836</t>
+          <t>139785</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>COPRODELI SAN MIGUEL</t>
+          <t>4001 DOS DE MAYO</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-12.02069</t>
+          <t>-12.06411</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>-77.13847</t>
+          <t>-77.15229</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>867</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>593997</t>
+          <t>140171</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2093 SANTA ROSA</t>
+          <t>5082 SARITA COLONIA</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-11.989659</t>
+          <t>-12.023593</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>-77.117276</t>
+          <t>-77.1332</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>956</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7879,32 +7879,32 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>594138</t>
+          <t>835840</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>5136 FERNANDO BELAUNDE TERRY</t>
+          <t>INNOVA SCHOOLS - CALLAO LEMOS</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-12.01088</t>
+          <t>-12.04917</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>-77.1358</t>
+          <t>-77.09473</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>962</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>594464</t>
+          <t>139870</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5031 CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-12.00561</t>
+          <t>-12.04287</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>-77.10623</t>
+          <t>-77.10235</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8003,42 +8003,42 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>594483</t>
+          <t>139912</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MI DIVINO NIÑO JESUS GUADALUPANO</t>
+          <t>4010 HERMANOS RAFAEL SAMUEL Y EMILIO MOISES GOMEZ PAQUIYAURI</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-12.04296</t>
+          <t>-11.97657</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>-77.11915</t>
+          <t>-77.12293</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8065,37 +8065,37 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>594727</t>
+          <t>140005</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>MUNDIAL</t>
+          <t>5042 JUAN FRANCISCO DE LA BODEGA Y QUADRA</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-12.06395</t>
+          <t>-12.04569</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>-77.13942</t>
+          <t>-77.11355</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8127,37 +8127,37 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>594850</t>
+          <t>513788</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SOR MARIA ROSA DE JESUS</t>
+          <t>SACO OLIVEROS APEIRON</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-12.06397</t>
+          <t>-12.026927</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>-77.13956</t>
+          <t>-77.093075</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8189,37 +8189,37 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>594949</t>
+          <t>516051</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN DE OQUENDO</t>
+          <t>ANGELES DE FATIMA SECUNDARIA</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-11.97002</t>
+          <t>-12.05482</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>-77.12221</t>
+          <t>-77.10704</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>129</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8251,37 +8251,37 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>594987</t>
+          <t>862310</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>INGENIERIA OQUENDO</t>
+          <t>AVE MARIA</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-11.97686</t>
+          <t>-12.06174</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>-77.11505</t>
+          <t>-77.13508</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8313,37 +8313,37 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>595034</t>
+          <t>141062</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FRANCISCO DE ZELA</t>
+          <t>BEATA ANA MARIA JAVOUHEY</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-12.01256</t>
+          <t>-12.03284</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>-77.09765</t>
+          <t>-77.09672</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>393</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8375,32 +8375,32 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>595072</t>
+          <t>595963</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CRISTIANO EMANUEL</t>
+          <t>BLAS PASCAL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-12.02556</t>
+          <t>-11.97584</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>-77.1339</t>
+          <t>-77.11408</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>816</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>595425</t>
+          <t>854329</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>5139 LAS COLINAS</t>
+          <t>INNOVA SCHOOLS - CALLAO SANTA ROSA</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-12.00322</t>
+          <t>-12.01167</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>-77.1015</t>
+          <t>-77.10567</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8499,32 +8499,32 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>595473</t>
+          <t>139479</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SAN JUAN EL BAUTISTA</t>
+          <t>JUAN INGUNZA VALDIVIA</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-11.94282</t>
+          <t>-12.01202</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>-77.13539</t>
+          <t>-77.0979</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8561,32 +8561,32 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>595883</t>
+          <t>140128</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>COPRODELI MONSEÑOR RICARDO DURAND</t>
+          <t>5033 LAS 200 MILLAS</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-11.996618</t>
+          <t>-11.9944</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>-77.123783</t>
+          <t>-77.1235</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>595963</t>
+          <t>141038</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>BLAS PASCAL</t>
+          <t>SAN JOSE HERMANOS MARISTAS</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-11.97584</t>
+          <t>-12.05654</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>-77.11408</t>
+          <t>-77.12863</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>852</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8685,37 +8685,37 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>595996</t>
+          <t>139889</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MATER PURISSIMA</t>
+          <t>5019 AUGUSTO CAZORLA</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-12.06235</t>
+          <t>-12.05306</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>-77.14369</t>
+          <t>-77.13395</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8747,32 +8747,32 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>608461</t>
+          <t>140500</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>INTELLECTUM SANTA ISABEL</t>
+          <t>JUNIOR CESAR DE LOS RIOS</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-12.051671</t>
+          <t>-12.05347</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>-77.111585</t>
+          <t>-77.12979</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>869</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8809,32 +8809,32 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>618115</t>
+          <t>140576</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SAGRADO NIÑO JESUS CHAPERITO</t>
+          <t>SANTA CRUZ</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-11.97775</t>
+          <t>-12.03214</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>-77.11459</t>
+          <t>-77.09748</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8871,37 +8871,37 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>624791</t>
+          <t>139403</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MARIA REINA DE CORAZONES</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-12.03402</t>
+          <t>-12.0218</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>-77.09815</t>
+          <t>-77.1368</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>135</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8933,37 +8933,37 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>651713</t>
+          <t>140213</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SAINT MARIA MAGDALENA' S KINDER</t>
+          <t>5085 RAMIRO PRIALE PRIALE</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-12.01739</t>
+          <t>-12.01514</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>-77.09376</t>
+          <t>-77.09056</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8995,32 +8995,32 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>691177</t>
+          <t>139907</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SAN BENITO DE OQUENDO S.A.C.</t>
+          <t>REPUBLICA DE VENEZUELA</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-11.977969</t>
+          <t>-12.05177</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>-77.122927</t>
+          <t>-77.13086</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>814</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9057,32 +9057,32 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>722334</t>
+          <t>140114</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA ASUNCION</t>
+          <t>5074 ALCIDES SPELUCIN VEGA</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-11.98632</t>
+          <t>-12.00959</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>-77.12007</t>
+          <t>-77.09624</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9119,32 +9119,32 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>748391</t>
+          <t>140246</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>TALENTUS SCHOOL</t>
+          <t>5095 JULIO RAMON RIBEYRO</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-12.00635</t>
+          <t>-12.0253</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>-77.10346</t>
+          <t>-77.0965</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9181,32 +9181,32 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>828934</t>
+          <t>140251</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>82 PASTORCITOS DE OQUENDO</t>
+          <t>5097 SAN JUAN MACIAS</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>-11.9779</t>
+          <t>-11.99755</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>-77.12332</t>
+          <t>-77.11748</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9243,37 +9243,37 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>833167</t>
+          <t>140034</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MARILLAC SCHOOL</t>
+          <t>5048 MARISCAL RAMON CASTILLA</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>-12.01791</t>
+          <t>-12.04143</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>-77.09319</t>
+          <t>-77.12345</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9305,32 +9305,32 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>835840</t>
+          <t>139747</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CALLAO LEMOS</t>
+          <t>112 MEDALLITA MILAGROSA</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>-12.04917</t>
+          <t>-11.99638</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>-77.09473</t>
+          <t>-77.11823</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>207</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9367,37 +9367,37 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>846103</t>
+          <t>142269</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>5155 BICENTENARIO LAS DELICIAS DE OQUENDO</t>
+          <t>EL NIÑO DOCTORCITO</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>-11.98181</t>
+          <t>-12.02372</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>-77.11578</t>
+          <t>-77.09821</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>162</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9429,37 +9429,37 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>851533</t>
+          <t>143363</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>DIEGO THOMSON</t>
+          <t>ANGELES DE FATIMA</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>-12.05859</t>
+          <t>-12.055242</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>-77.13059</t>
+          <t>-77.107548</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>102</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9491,32 +9491,32 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>853886</t>
+          <t>142009</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>STAR TALENT PERU SCHOOL</t>
+          <t>BERTOLT BRECHT</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>-12.017783</t>
+          <t>-12.04986</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>-77.09138</t>
+          <t>-77.07887</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9553,32 +9553,32 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>854329</t>
+          <t>140133</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CALLAO SANTA ROSA</t>
+          <t>5026 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-12.01167</t>
+          <t>-12.01984</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>-77.10567</t>
+          <t>-77.09149</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9615,32 +9615,32 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>861589</t>
+          <t>140270</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>UNIVERSIA DEL CALLAO</t>
+          <t>POLITECNICO NACIONAL DEL CALLAO</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-12.00607</t>
+          <t>-12.044294</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>-77.09687</t>
+          <t>-77.099361</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9677,32 +9677,32 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>862310</t>
+          <t>594483</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>AVE MARIA</t>
+          <t>MI DIVINO NIÑO JESUS GUADALUPANO</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>-12.06174</t>
+          <t>-12.04296</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>-77.13508</t>
+          <t>-77.11915</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9739,32 +9739,32 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>140350</t>
+          <t>828934</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>PAEBA PILOTO REGIONAL DE EXCELENCIA</t>
+          <t>82 PASTORCITOS DE OQUENDO</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>-11.93978</t>
+          <t>-11.9779</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>-77.13185</t>
+          <t>-77.12332</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/CALLAO-CALLAO-CALLAO.xlsx
+++ b/ZonasEscolares/excels/CALLAO-CALLAO-CALLAO.xlsx
@@ -501,42 +501,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>140350</t>
+          <t>862310</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PAEBA PILOTO REGIONAL DE EXCELENCIA</t>
+          <t>AVE MARIA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.93978</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.13185</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.06174</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-77.13508</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>139728</t>
+          <t>861589</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>109 DIVINO JESUS</t>
+          <t>UNIVERSIA DEL CALLAO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.02312</t>
+          <t>360</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.09538</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-12.00607</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.09687</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>139851</t>
+          <t>854329</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>92 LOS NIÑITOS DE SANTA ROSA</t>
+          <t>INNOVA SCHOOLS - CALLAO SANTA ROSA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.05338</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.1198</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-12.01167</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.10567</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>139417</t>
+          <t>853886</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>071 RETOÑITOS DE LA VIRGEN DE GUADALUPE</t>
+          <t>STAR TALENT PERU SCHOOL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.043279</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.113979</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>-12.017783</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.09138</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>139441</t>
+          <t>851533</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>073 SEÑOR DE LA MISERICORDIA</t>
+          <t>DIEGO THOMSON</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.01661</t>
+          <t>278</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.09039</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>-12.05859</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.13059</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>139484</t>
+          <t>846103</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>78 AMIGUITOS DE SAN MARTIN</t>
+          <t>5155 BICENTENARIO LAS DELICIAS DE OQUENDO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.03371</t>
+          <t>395</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.09884</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>-11.98181</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.11578</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>139506</t>
+          <t>835840</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>80 LOS NIÑOS DE JESUS</t>
+          <t>INNOVA SCHOOLS - CALLAO LEMOS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.99643</t>
+          <t>962</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.1244</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>-12.04917</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.09473</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>139714</t>
+          <t>833167</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>100 VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>MARILLAC SCHOOL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.00085</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.10856</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>-12.01791</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.09319</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>140147</t>
+          <t>828934</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5078 JOSE A. QUIÑONES GONZALES</t>
+          <t>82 PASTORCITOS DE OQUENDO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.0528</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.12218</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>-11.9779</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.12332</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>142212</t>
+          <t>748391</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LIBERTADOR SIMON BOLIVAR</t>
+          <t>TALENTUS SCHOOL</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.06242</t>
+          <t>603</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.14131</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>-12.00635</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.10346</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>171822</t>
+          <t>722334</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ESCUELA DEL BUEN SABER</t>
+          <t>NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.9976</t>
+          <t>269</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.1081</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-11.98632</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.12007</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>553171</t>
+          <t>691177</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>137 FEDERICO VILLARREAL</t>
+          <t>SAN BENITO DE OQUENDO S.A.C.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.9786</t>
+          <t>690</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.1197</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-11.977969</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.122927</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>595883</t>
+          <t>651713</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>COPRODELI MONSEÑOR RICARDO DURAND</t>
+          <t>SAINT MARIA MAGDALENA' S KINDER</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.996618</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.123783</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>-12.01739</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.09376</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>140091</t>
+          <t>624791</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5076 NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>MARIA REINA DE CORAZONES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.9433</t>
+          <t>484</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.1326</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>-12.03402</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>-77.09815</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>139422</t>
+          <t>618115</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69 MARIA AUXILIADORA</t>
+          <t>SAGRADO NIÑO JESUS CHAPERITO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.03731</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.09664</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>-11.97775</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.11459</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>139733</t>
+          <t>608461</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>111 MI PEQUEÑO PARAISO</t>
+          <t>INTELLECTUM SANTA ISABEL</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.02819</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.09627</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>-12.051671</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.111585</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1493,37 +1493,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>139752</t>
+          <t>595996</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>115 VIRGEN DE GUADALUPE</t>
+          <t>MATER PURISSIMA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.02384</t>
+          <t>190</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.09334</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>-12.06235</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.14369</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>140388</t>
+          <t>595963</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>98 NIÑITO JESUS DE PRAGA</t>
+          <t>BLAS PASCAL</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.94224</t>
+          <t>816</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.13399</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>-11.97584</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.11408</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>594464</t>
+          <t>595883</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>COPRODELI MONSEÑOR RICARDO DURAND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.00561</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.10623</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>-11.996618</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.123783</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>748391</t>
+          <t>595473</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TALENTUS SCHOOL</t>
+          <t>SAN JUAN EL BAUTISTA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.00635</t>
+          <t>674</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.10346</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>-11.94282</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.13539</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>139380</t>
+          <t>595425</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>64 DIVINO NIÑO JESUS</t>
+          <t>5139 LAS COLINAS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.05287</t>
+          <t>694</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.13031</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>-12.00322</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.1015</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>139455</t>
+          <t>595072</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>76 MI AMIGO JESUS</t>
+          <t>CRISTIANO EMANUEL</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.04083</t>
+          <t>304</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.12267</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>-12.02556</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.1339</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1865,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>139460</t>
+          <t>595034</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>77 SANTISIMA VIRGEN DEL CARMEN</t>
+          <t>FRANCISCO DE ZELA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.01001</t>
+          <t>277</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.10459</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>-12.01256</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.09765</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>139587</t>
+          <t>594987</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>94 MIGUEL GRAU</t>
+          <t>INGENIERIA OQUENDO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.04614</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.10393</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>-11.97686</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.11505</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>139605</t>
+          <t>594949</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>84 NIÑA MARIA</t>
+          <t>SAN AGUSTIN DE OQUENDO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.0159</t>
+          <t>471</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.10013</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>-11.97002</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.12221</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,37 +2051,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>139610</t>
+          <t>594850</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>85 NIÑO JESUS</t>
+          <t>SOR MARIA ROSA DE JESUS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.01256</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.10178</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>-12.06397</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.13956</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>139634</t>
+          <t>594727</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>87 SANTA ROSA</t>
+          <t>MUNDIAL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.01653</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.1014</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>-12.06395</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.13942</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,42 +2175,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>141811</t>
+          <t>594483</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>COPRODELI SAN VICENTE</t>
+          <t>MI DIVINO NIÑO JESUS GUADALUPANO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.01274</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.13646</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>-12.04296</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.11915</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>722334</t>
+          <t>594464</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA ASUNCION</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.98632</t>
+          <t>723</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.12007</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>-12.00561</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.10623</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>140190</t>
+          <t>594138</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>5080 SOR ANA DE LOS ANGELES</t>
+          <t>5136 FERNANDO BELAUNDE TERRY</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.01107</t>
+          <t>478</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.10339</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>-12.01088</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>-77.1358</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>139865</t>
+          <t>593997</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>JUAN PABLO II</t>
+          <t>2093 SANTA ROSA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.02478</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.12934</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>-11.989659</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.117276</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>140883</t>
+          <t>593836</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>JORDAN DE JESUS</t>
+          <t>COPRODELI SAN MIGUEL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-11.99636</t>
+          <t>601</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.12294</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>-12.02069</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.13847</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>140920</t>
+          <t>593662</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ENMANUEL</t>
+          <t>3090 FRANCO PERUANO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-11.998</t>
+          <t>567</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.12131</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-12.0318</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.0979</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>332877</t>
+          <t>593558</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE X</t>
+          <t>MARIA REINA DE LA ESPERANZA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.035485</t>
+          <t>559</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.095162</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-12.0022</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.10862</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>139629</t>
+          <t>590606</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>86 SEÑOR DE LOS MILAGROS</t>
+          <t>BELLA UNION II</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.01318</t>
+          <t>453</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.10303</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>-12.04617</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.1136</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>139950</t>
+          <t>580805</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>5003 VIRGEN DE LA INMACULADA CONCEPCION</t>
+          <t>SAN AGUSTIN DE LOS SAIRES</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.06318</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.14344</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>-11.967735</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.123003</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>139974</t>
+          <t>580768</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>5006 ALBERTO SECADA</t>
+          <t>AMADEUS MOZART DE OQUENDO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.05868</t>
+          <t>460</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.14027</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>-11.98065</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.11527</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>140915</t>
+          <t>567941</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CORAZON DE JESUS</t>
+          <t>JESUS ES MI LUZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.02103</t>
+          <t>334</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.09283</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-12.0558</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.11271</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>139511</t>
+          <t>553171</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4008 NUESTRA SEÑORA DE FATIMA</t>
+          <t>137 FEDERICO VILLARREAL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.05278</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.10824</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>-11.9786</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.1197</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,37 +2919,37 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>139926</t>
+          <t>516051</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4011 LA TABOADA DE LAS FRESAS</t>
+          <t>ANGELES DE FATIMA SECUNDARIA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.00276</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.11283</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>-12.05482</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.10704</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>846103</t>
+          <t>513788</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>5155 BICENTENARIO LAS DELICIAS DE OQUENDO</t>
+          <t>SACO OLIVEROS APEIRON</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-11.98181</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.11578</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>-12.026927</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.093075</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>139375</t>
+          <t>508800</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>62 PASITOS DE JESUS</t>
+          <t>SAN LUIS GONZAGA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.05516</t>
+          <t>436</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.13472</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>-12.01823</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.09402</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>140086</t>
+          <t>332877</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>5010 VIRGEN DE GUADALUPE</t>
+          <t>LUIS ENRIQUE X</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.04644</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.10265</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>-12.035485</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.095162</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>580768</t>
+          <t>300490</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AMADEUS MOZART DE OQUENDO</t>
+          <t>TRILCE CALLAO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-11.98065</t>
+          <t>418</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.11527</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>-12.05939</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.1329</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>590606</t>
+          <t>171822</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BELLA UNION II</t>
+          <t>ESCUELA DEL BUEN SABER</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.04617</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.1136</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>-11.9976</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.1081</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>142453</t>
+          <t>143363</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>EL MUNDO DE LOS NIÑOS</t>
+          <t>ANGELES DE FATIMA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-11.99594</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.12035</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-12.055242</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.107548</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>594987</t>
+          <t>142453</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>INGENIERIA OQUENDO</t>
+          <t>EL MUNDO DE LOS NIÑOS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-11.97686</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.11505</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-11.99594</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.12035</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,37 +3415,37 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>595996</t>
+          <t>142269</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MATER PURISSIMA</t>
+          <t>EL NIÑO DOCTORCITO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.06235</t>
+          <t>162</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.14369</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>-12.02372</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.09821</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>139832</t>
+          <t>142212</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>5001 LUISA DE SABOGAL</t>
+          <t>LIBERTADOR SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.06053</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-77.14445</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>-12.06242</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.14131</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,37 +3539,37 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>141161</t>
+          <t>142066</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MARIA REINA DE CORAZONES</t>
+          <t>MI JESUS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.04606</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-77.11013</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>-12.04966</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.10399</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>141547</t>
+          <t>142009</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ALBORADA</t>
+          <t>BERTOLT BRECHT</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.05911</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-77.13353</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-12.04986</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.07887</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>861589</t>
+          <t>141811</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UNIVERSIA DEL CALLAO</t>
+          <t>COPRODELI SAN VICENTE</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.00607</t>
+          <t>359</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-77.09687</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>-12.01274</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.13646</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>508800</t>
+          <t>141707</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SAN LUIS GONZAGA</t>
+          <t>ALFREDO REBAZA ACOSTA DE LOS JAZMINES</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.01823</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-77.09402</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>-12.00359</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.10818</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>567941</t>
+          <t>141613</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>JESUS ES MI LUZ</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12.0558</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-77.11271</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>-12.0582</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.13813</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>595034</t>
+          <t>141590</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FRANCISCO DE ZELA</t>
+          <t>JESUS SALVADOR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-12.01256</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-77.09765</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>-12.0023</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.10136</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>139827</t>
+          <t>141547</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>5032 ENRIQUE DEL HORME</t>
+          <t>ALBORADA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-12.05201</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-77.10136</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>-12.05911</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.13353</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>140897</t>
+          <t>141420</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FLORENCE NIGHTINGALE</t>
+          <t>COPRODELI AGUSTIN HIPONA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-12.01716</t>
+          <t>645</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-77.09765</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>-12.02325</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.134864</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>851533</t>
+          <t>141255</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>DIEGO THOMSON</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-12.05859</t>
+          <t>346</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-77.13059</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>-11.93995</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.13217</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,37 +4097,37 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>141590</t>
+          <t>141175</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>JESUS SALVADOR</t>
+          <t>VIRGEN DE CHAPI</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-12.0023</t>
+          <t>347</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-77.10136</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-12.00975</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.10239</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>141613</t>
+          <t>141161</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>MARIA REINA DE CORAZONES</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-12.0582</t>
+          <t>397</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-77.13813</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>-12.04606</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.11013</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>139808</t>
+          <t>141081</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>4007 VIRGEN DEL PILAR</t>
+          <t>JUANITO BOSCO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-12.0549</t>
+          <t>446</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-77.11255</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>-12.02437</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.13332</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>140109</t>
+          <t>141062</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>5075 INCA GARCILASO DE LA VEGA</t>
+          <t>BEATA ANA MARIA JAVOUHEY</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-12.03424</t>
+          <t>393</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-77.09829</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>-12.03284</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.09672</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,42 +4345,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>140289</t>
+          <t>141038</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>JORGE BASADRE GROHMAN</t>
+          <t>SAN JOSE HERMANOS MARISTAS</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-12.06236</t>
+          <t>852</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-77.13567</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>-12.05654</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.12863</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>594949</t>
+          <t>140920</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN DE OQUENDO</t>
+          <t>ENMANUEL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-11.97002</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-77.12221</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>-11.998</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.12131</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>595072</t>
+          <t>140915</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CRISTIANO EMANUEL</t>
+          <t>CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-12.02556</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-77.1339</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>-12.02103</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.09283</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>139894</t>
+          <t>140897</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>5024 FRANCISCO MIRO QUESADA CANTUARIAS</t>
+          <t>FLORENCE NIGHTINGALE</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-12.05389</t>
+          <t>327</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-77.12877</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>-12.01716</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.09765</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>140232</t>
+          <t>140883</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>5092 SANTA ROSA DE LIMA</t>
+          <t>JORDAN DE JESUS</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-12.02346</t>
+          <t>219</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-77.10116</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>-11.99636</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.12294</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>140784</t>
+          <t>140816</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SAN BENITO DE PALERMO</t>
+          <t>JEAN CALVIN LEFRANC</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-11.99852</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-77.11808</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>-12.00717</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.10353</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>140816</t>
+          <t>140784</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>JEAN CALVIN LEFRANC</t>
+          <t>SAN BENITO DE PALERMO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-12.00717</t>
+          <t>417</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-77.10353</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-11.99852</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.11808</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,42 +4779,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>139648</t>
+          <t>140760</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>5023 ABELARDO GAMARRA</t>
+          <t>JERUSALEN</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-12.05689</t>
+          <t>274</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-77.12657</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>-12.04123</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.10048</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>140067</t>
+          <t>140736</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>5037 ALMIRANTE MIGUEL GRAU</t>
+          <t>MERIDIONAL SANTA ANA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-12.02282</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-77.13738</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>-12.04089</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.1249</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>140736</t>
+          <t>140675</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MERIDIONAL SANTA ANA</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-12.04089</t>
+          <t>347</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-77.1249</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>-12.02196</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.09209</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4965,37 +4965,37 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>140760</t>
+          <t>140656</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>JERUSALEN</t>
+          <t>NIÑO JESUS MARISCAL CHAPERITO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-12.04123</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-77.10048</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-12.02095</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.09563</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>141175</t>
+          <t>140576</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>VIRGEN DE CHAPI</t>
+          <t>SANTA CRUZ</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.00975</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-77.10239</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>-12.03214</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.09748</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>141255</t>
+          <t>140538</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-11.93995</t>
+          <t>821</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-77.13217</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>-12.01704</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.09554</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>594138</t>
+          <t>140500</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>5136 FERNANDO BELAUNDE TERRY</t>
+          <t>JUNIOR CESAR DE LOS RIOS</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-12.01088</t>
+          <t>869</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-77.1358</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>-12.05347</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.12979</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>608461</t>
+          <t>140487</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>INTELLECTUM SANTA ISABEL</t>
+          <t>JOSE GALVEZ</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-12.051671</t>
+          <t>377</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-77.111585</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>-12.05679</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.13601</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>624791</t>
+          <t>140411</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MARIA REINA DE CORAZONES</t>
+          <t>JUAN LINARES ROJAS</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-12.03402</t>
+          <t>792</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-77.09815</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>-11.97227</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.1229</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>140010</t>
+          <t>140388</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>5046 JOSE GALVEZ EGUSQUIZA</t>
+          <t>98 NIÑITO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-12.04398</t>
+          <t>310</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-77.12434</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>-11.94224</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.13399</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>593662</t>
+          <t>140350</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>3090 FRANCO PERUANO</t>
+          <t>PAEBA PILOTO REGIONAL DE EXCELENCIA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-12.0318</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-77.0979</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>-11.93978</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.13185</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>140053</t>
+          <t>140294</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>5036 RAFAEL BELAUNDE DIEZ CANSECO</t>
+          <t>5099 RICARDO PALMA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-12.03769</t>
+          <t>687</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-77.09641</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>-12.02017</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.09931</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,42 +5523,42 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>140227</t>
+          <t>140289</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>5089 VIRGEN MARIA</t>
+          <t>JORGE BASADRE GROHMAN</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-11.99932</t>
+          <t>410</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-77.10861</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>-12.06236</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.13567</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>580805</t>
+          <t>140270</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN DE LOS SAIRES</t>
+          <t>POLITECNICO NACIONAL DEL CALLAO</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-11.967735</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-77.123003</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>-12.044294</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.099361</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5647,42 +5647,42 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>593558</t>
+          <t>140265</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MARIA REINA DE LA ESPERANZA</t>
+          <t>HEROINAS TOLEDO</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-12.0022</t>
+          <t>449</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-77.10862</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>-12.06186</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.13567</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>139766</t>
+          <t>140251</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>5040 PEDRO RUIZ</t>
+          <t>5097 SAN JUAN MACIAS</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-12.05041</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-77.10393</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>-11.99755</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.11748</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>140675</t>
+          <t>140246</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>LOS OLIVOS</t>
+          <t>5095 JULIO RAMON RIBEYRO</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-12.02196</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-77.09209</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>-12.0253</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.0965</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>853886</t>
+          <t>140232</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>STAR TALENT PERU SCHOOL</t>
+          <t>5092 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-12.017783</t>
+          <t>521</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-77.09138</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>-12.02346</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.10116</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>140152</t>
+          <t>140227</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>5079 JORGE CHAVEZ DARNELL</t>
+          <t>5089 VIRGEN MARIA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-12.0174</t>
+          <t>722</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-77.09675</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>-11.99932</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.10861</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>140656</t>
+          <t>140213</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>NIÑO JESUS MARISCAL CHAPERITO</t>
+          <t>5085 RAMIRO PRIALE PRIALE</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-12.02095</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-77.09563</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>-12.01514</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.09056</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>618115</t>
+          <t>140208</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SAGRADO NIÑO JESUS CHAPERITO</t>
+          <t>5084 CARLOS PHILLIPS</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-11.97775</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-77.11459</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-12.017055</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.090428</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,37 +6081,37 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>140190</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MI JESUS</t>
+          <t>5080 SOR ANA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-12.04966</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-77.10399</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-12.01107</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-77.10339</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6143,37 +6143,37 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>594727</t>
+          <t>140185</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>MUNDIAL</t>
+          <t>5083 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-12.06395</t>
+          <t>732</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-77.13942</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-12.01038</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-77.10504</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6205,37 +6205,37 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>594850</t>
+          <t>140171</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SOR MARIA ROSA DE JESUS</t>
+          <t>5082 SARITA COLONIA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-12.06397</t>
+          <t>956</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-77.13956</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-12.023593</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-77.1332</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>139846</t>
+          <t>140152</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>4006 SANTA ROSA DE AMERICA</t>
+          <t>5079 JORGE CHAVEZ DARNELL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-12.05609</t>
+          <t>626</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-77.11615</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>-12.0174</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-77.09675</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>141420</t>
+          <t>140147</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>COPRODELI AGUSTIN HIPONA</t>
+          <t>5078 JOSE A. QUIÑONES GONZALES</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-12.02325</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-77.134864</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>-12.0528</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-77.12218</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>593997</t>
+          <t>140133</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2093 SANTA ROSA</t>
+          <t>5026 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-11.989659</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-77.117276</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-12.01984</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-77.09149</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>140185</t>
+          <t>140128</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>5083 SAN MARTIN DE PORRES</t>
+          <t>5033 LAS 200 MILLAS</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-12.01038</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-77.10504</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>-11.9944</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.1235</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>593836</t>
+          <t>140114</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>COPRODELI SAN MIGUEL</t>
+          <t>5074 ALCIDES SPELUCIN VEGA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-12.02069</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-77.13847</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>-12.00959</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.09624</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>691177</t>
+          <t>140109</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SAN BENITO DE OQUENDO S.A.C.</t>
+          <t>5075 INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-11.977969</t>
+          <t>523</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-77.122927</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>-12.03424</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.09829</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>139969</t>
+          <t>140091</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>5005 GENMO DON JOSE DE SAN MARTIN</t>
+          <t>5076 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-12.05954</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-77.13717</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>-11.9433</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-77.1326</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>595425</t>
+          <t>140086</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>5139 LAS COLINAS</t>
+          <t>5010 VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-12.00322</t>
+          <t>392</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-77.1015</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>-12.04644</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-77.10265</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>140294</t>
+          <t>140067</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>5099 RICARDO PALMA</t>
+          <t>5037 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-12.02017</t>
+          <t>534</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-77.09931</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>-12.02282</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-77.13738</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6825,32 +6825,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>139988</t>
+          <t>140053</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>5007 NUESTRA SEÑORA DE GUADALUPE</t>
+          <t>5036 RAFAEL BELAUNDE DIEZ CANSECO</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-12.05276</t>
+          <t>664</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-77.1402</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>-12.03769</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-77.09641</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6887,32 +6887,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>140487</t>
+          <t>140048</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>JOSE GALVEZ</t>
+          <t>5049 EMMA DETTMANN DE GUTIERREZ</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-12.05679</t>
+          <t>781</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-77.13601</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>-12.05066</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-77.09526</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>141081</t>
+          <t>140034</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>JUANITO BOSCO</t>
+          <t>5048 MARISCAL RAMON CASTILLA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-12.02437</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-77.13332</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>-12.04143</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-77.12345</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7011,32 +7011,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>139931</t>
+          <t>140010</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>4016 NESTOR GAMBETA BONATTI</t>
+          <t>5046 JOSE GALVEZ EGUSQUIZA</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-12.0434</t>
+          <t>511</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-77.1137</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>-12.04398</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-77.12434</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7073,37 +7073,37 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>651713</t>
+          <t>140005</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SAINT MARIA MAGDALENA' S KINDER</t>
+          <t>5042 JUAN FRANCISCO DE LA BODEGA Y QUADRA</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-12.01739</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-77.09376</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-12.04569</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-77.11355</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7135,37 +7135,37 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>833167</t>
+          <t>139988</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MARILLAC SCHOOL</t>
+          <t>5007 NUESTRA SEÑORA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-12.01791</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-77.09319</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-12.05276</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-77.1402</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7197,32 +7197,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>139945</t>
+          <t>139974</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>4018 ABRAHAM VALDELOMAR</t>
+          <t>5006 ALBERTO SECADA</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-12.04283</t>
+          <t>329</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-77.11144</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>-12.05868</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-77.14027</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7259,32 +7259,32 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>141707</t>
+          <t>139969</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>ALFREDO REBAZA ACOSTA DE LOS JAZMINES</t>
+          <t>5005 GENMO DON JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-12.00359</t>
+          <t>723</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>-77.10818</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>-12.05954</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-77.13717</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7321,32 +7321,32 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>140411</t>
+          <t>139950</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>JUAN LINARES ROJAS</t>
+          <t>5003 VIRGEN DE LA INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-11.97227</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-77.1229</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>-12.06318</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-77.14344</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7383,32 +7383,32 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>595473</t>
+          <t>139945</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>SAN JUAN EL BAUTISTA</t>
+          <t>4018 ABRAHAM VALDELOMAR</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-11.94282</t>
+          <t>765</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-77.13539</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>-12.04283</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-77.11144</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7445,32 +7445,32 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>140208</t>
+          <t>139931</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>5084 CARLOS PHILLIPS</t>
+          <t>4016 NESTOR GAMBETA BONATTI</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-12.017055</t>
+          <t>789</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-77.090428</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>-12.0434</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-77.1137</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7507,32 +7507,32 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>300490</t>
+          <t>139926</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>TRILCE CALLAO</t>
+          <t>4011 LA TABOADA DE LAS FRESAS</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-12.05939</t>
+          <t>430</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-77.1329</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>-12.00276</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-77.11283</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7569,32 +7569,32 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>140048</t>
+          <t>139912</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>5049 EMMA DETTMANN DE GUTIERREZ</t>
+          <t>4010 HERMANOS RAFAEL SAMUEL Y EMILIO MOISES GOMEZ PAQUIYAURI</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-12.05066</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>-77.09526</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>-11.97657</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-77.12293</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7631,32 +7631,32 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>140538</t>
+          <t>139907</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>NIÑO JESUS DE PRAGA</t>
+          <t>REPUBLICA DE VENEZUELA</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-12.01704</t>
+          <t>814</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>-77.09554</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>-12.05177</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-77.13086</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7693,37 +7693,37 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>140265</t>
+          <t>139894</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>HEROINAS TOLEDO</t>
+          <t>5024 FRANCISCO MIRO QUESADA CANTUARIAS</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-12.06186</t>
+          <t>539</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>-77.13567</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>-12.05389</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-77.12877</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7755,37 +7755,37 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>139785</t>
+          <t>139889</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>4001 DOS DE MAYO</t>
+          <t>5019 AUGUSTO CAZORLA</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-12.06411</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>-77.15229</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>-12.05306</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-77.13395</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>140171</t>
+          <t>139870</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>5082 SARITA COLONIA</t>
+          <t>5031 CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-12.023593</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>-77.1332</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>-12.04287</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-77.10235</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7879,32 +7879,32 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>835840</t>
+          <t>139865</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CALLAO LEMOS</t>
+          <t>JUAN PABLO II</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-12.04917</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>-77.09473</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>-12.02478</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-77.12934</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7941,42 +7941,42 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>139870</t>
+          <t>139851</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>5031 CESAR VALLEJO</t>
+          <t>92 LOS NIÑITOS DE SANTA ROSA</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-12.04287</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>-77.10235</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>-12.05338</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-77.1198</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8003,32 +8003,32 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>139912</t>
+          <t>139846</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>4010 HERMANOS RAFAEL SAMUEL Y EMILIO MOISES GOMEZ PAQUIYAURI</t>
+          <t>4006 SANTA ROSA DE AMERICA</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-11.97657</t>
+          <t>608</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>-77.12293</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>-12.05609</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-77.11615</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8065,32 +8065,32 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>140005</t>
+          <t>139832</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>5042 JUAN FRANCISCO DE LA BODEGA Y QUADRA</t>
+          <t>5001 LUISA DE SABOGAL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-12.04569</t>
+          <t>403</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>-77.11355</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>-12.06053</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-77.14445</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>513788</t>
+          <t>139827</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS APEIRON</t>
+          <t>5032 ENRIQUE DEL HORME</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-12.026927</t>
+          <t>425</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>-77.093075</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>-12.05201</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-77.10136</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8189,42 +8189,42 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>516051</t>
+          <t>139808</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ANGELES DE FATIMA SECUNDARIA</t>
+          <t>4007 VIRGEN DEL PILAR</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-12.05482</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>-77.10704</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>-12.0549</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-77.11255</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8251,37 +8251,37 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>862310</t>
+          <t>139785</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>AVE MARIA</t>
+          <t>4001 DOS DE MAYO</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-12.06174</t>
+          <t>867</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>-77.13508</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>-12.06411</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-77.15229</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8313,32 +8313,32 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>141062</t>
+          <t>139766</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>BEATA ANA MARIA JAVOUHEY</t>
+          <t>5040 PEDRO RUIZ</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-12.03284</t>
+          <t>501</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>-77.09672</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>-12.05041</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-77.10393</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8375,32 +8375,32 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>595963</t>
+          <t>139752</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>BLAS PASCAL</t>
+          <t>115 VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-11.97584</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>-77.11408</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>-12.02384</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-77.09334</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>854329</t>
+          <t>139747</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CALLAO SANTA ROSA</t>
+          <t>112 MEDALLITA MILAGROSA</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-12.01167</t>
+          <t>207</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>-77.10567</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>-11.99638</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-77.11823</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8499,32 +8499,32 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>139479</t>
+          <t>139733</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>JUAN INGUNZA VALDIVIA</t>
+          <t>111 MI PEQUEÑO PARAISO</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-12.01202</t>
+          <t>298</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>-77.0979</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>-12.02819</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-77.09627</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8561,32 +8561,32 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>140128</t>
+          <t>139728</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>5033 LAS 200 MILLAS</t>
+          <t>109 DIVINO JESUS</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-11.9944</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>-77.1235</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>-12.02312</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-77.09538</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>141038</t>
+          <t>139714</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SAN JOSE HERMANOS MARISTAS</t>
+          <t>100 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-12.05654</t>
+          <t>249</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>-77.12863</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>-12.00085</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-77.10856</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8685,42 +8685,42 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>139889</t>
+          <t>139648</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>5019 AUGUSTO CAZORLA</t>
+          <t>5023 ABELARDO GAMARRA</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-12.05306</t>
+          <t>568</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>-77.13395</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>-12.05689</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-77.12657</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8747,32 +8747,32 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>140500</t>
+          <t>139634</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>JUNIOR CESAR DE LOS RIOS</t>
+          <t>87 SANTA ROSA</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-12.05347</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>-77.12979</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>-12.01653</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-77.1014</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8809,32 +8809,32 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>140576</t>
+          <t>139629</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SANTA CRUZ</t>
+          <t>86 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-12.03214</t>
+          <t>336</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>-77.09748</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>-12.01318</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-77.10303</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8871,37 +8871,37 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>139403</t>
+          <t>139610</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>85 NIÑO JESUS</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-12.0218</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>-77.1368</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>-12.01256</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-77.10178</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8933,32 +8933,32 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>140213</t>
+          <t>139605</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>5085 RAMIRO PRIALE PRIALE</t>
+          <t>84 NIÑA MARIA</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-12.01514</t>
+          <t>304</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>-77.09056</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>-12.0159</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-77.10013</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8995,32 +8995,32 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>139907</t>
+          <t>139587</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>REPUBLICA DE VENEZUELA</t>
+          <t>94 MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-12.05177</t>
+          <t>294</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>-77.13086</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>-12.04614</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-77.10393</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9057,32 +9057,32 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>140114</t>
+          <t>139511</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>5074 ALCIDES SPELUCIN VEGA</t>
+          <t>4008 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-12.00959</t>
+          <t>428</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>-77.09624</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>-12.05278</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-77.10824</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9119,32 +9119,32 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>140246</t>
+          <t>139506</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>5095 JULIO RAMON RIBEYRO</t>
+          <t>80 LOS NIÑOS DE JESUS</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-12.0253</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>-77.0965</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>-11.99643</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-77.1244</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9181,32 +9181,32 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>140251</t>
+          <t>139484</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>5097 SAN JUAN MACIAS</t>
+          <t>78 AMIGUITOS DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>-11.99755</t>
+          <t>239</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>-77.11748</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>-12.03371</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-77.09884</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9243,32 +9243,32 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>140034</t>
+          <t>139479</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>5048 MARISCAL RAMON CASTILLA</t>
+          <t>JUAN INGUNZA VALDIVIA</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>-12.04143</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>-77.12345</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>-12.01202</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-77.0979</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9305,32 +9305,32 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>139747</t>
+          <t>139460</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>112 MEDALLITA MILAGROSA</t>
+          <t>77 SANTISIMA VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>-11.99638</t>
+          <t>271</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>-77.11823</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>-12.01001</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-77.10459</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9367,42 +9367,42 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>142269</t>
+          <t>139455</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>EL NIÑO DOCTORCITO</t>
+          <t>76 MI AMIGO JESUS</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>-12.02372</t>
+          <t>331</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>-77.09821</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>-12.04083</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-77.12267</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9429,37 +9429,37 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>143363</t>
+          <t>139441</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ANGELES DE FATIMA</t>
+          <t>073 SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>-12.055242</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>-77.107548</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>-12.01661</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-77.09039</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9491,32 +9491,32 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>142009</t>
+          <t>139422</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>BERTOLT BRECHT</t>
+          <t>69 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>-12.04986</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>-77.07887</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>-12.03731</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>-77.09664</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9553,32 +9553,32 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>140133</t>
+          <t>139417</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>5026 JOSE MARIA ARGUEDAS</t>
+          <t>071 RETOÑITOS DE LA VIRGEN DE GUADALUPE</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-12.01984</t>
+          <t>257</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>-77.09149</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>-12.043279</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>-77.113979</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9615,42 +9615,42 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>140270</t>
+          <t>139403</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>POLITECNICO NACIONAL DEL CALLAO</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-12.044294</t>
+          <t>135</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>-77.099361</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>-12.0218</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>-77.1368</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9677,42 +9677,42 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>594483</t>
+          <t>139380</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>MI DIVINO NIÑO JESUS GUADALUPANO</t>
+          <t>64 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>-12.04296</t>
+          <t>301</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>-77.11915</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>-12.05287</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.13031</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9739,32 +9739,32 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>828934</t>
+          <t>139375</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>82 PASTORCITOS DE OQUENDO</t>
+          <t>62 PASITOS DE JESUS</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>-11.9779</t>
+          <t>339</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>-77.12332</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-12.05516</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.13472</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">

--- a/ZonasEscolares/excels/CALLAO-CALLAO-CALLAO.xlsx
+++ b/ZonasEscolares/excels/CALLAO-CALLAO-CALLAO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
